--- a/Input example/inputExample_v1.4.0_PowerModuleAndCapacitor.xlsx
+++ b/Input example/inputExample_v1.4.0_PowerModuleAndCapacitor.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thomaslesaulnier/Documents/PFE/ENS_MERCE/PELCA_internal/Input example/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guillemet\Documents\PELCA_internal\Input example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83309458-565A-E140-9341-EE64E64354E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AB10869-8B06-4EEE-AC1C-938F99B06A06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4300" yWindow="-18520" windowWidth="28800" windowHeight="16260" tabRatio="649" xr2:uid="{A22A29AF-6D9D-7E4D-B999-57E82FA055BC}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="649" activeTab="1" xr2:uid="{A22A29AF-6D9D-7E4D-B999-57E82FA055BC}"/>
   </bookViews>
   <sheets>
     <sheet name="PELCA - Legend | License" sheetId="10" r:id="rId1"/>
@@ -720,13 +720,6 @@
   </si>
   <si>
     <t>Electricity cost (€/kWh)</t>
-  </si>
-  <si>
-    <t>A RU (Reference Unit) can include multiple units. For example:
-- RU: 4 NP-type capacitors
-- Unit: 1 NP-type capacitor
-The exchange flows for each RU are defined based on a single unit.
-If the RU consists of N units, this is indicated in the 'scaling factor' column of the last row by 1/N. This cell shows that the flows defined for one unit (in the column 'quantity') represent 1/N of the flows for the total RU. Therefore, the flows for the RU correspond to N times the flows of a single unit.</t>
   </si>
   <si>
     <t>/Users/username/Downloads/ecoinvent 3.9.1_cutoff_ecoSpold02/datasets</t>
@@ -1035,6 +1028,13 @@
   </si>
   <si>
     <t>Version</t>
+  </si>
+  <si>
+    <t>A RU (Reference Unit) can include multiple units. For example:
+- RU: 4 NP-type capacitors
+- Unit: 1 NP-type capacitor
+The exchange flows for each RU are defined based on a single unit.
+If the RU consists of N units, this is indicated in the 'scaling factor' column of the last row by N. This cell shows that the flows defined for a single unit (in the column 'quantity') represent 1/N of the flows for the total RU. Therefore, the flows for the total RU correspond to N times the flows of a single unit. Example: the RU is a power switch embedding 4 power dice in parallel --&gt; the listed exchanges corresponds to the flows for the manufacturing of 1 power die ; the cell of column D ('scaling factor'), last row indicates 4 ; the cell of column E ('amount'), last row automatically indicates 1/N = 0,25 ; this means that the amounts of all the listed flows will be divided by 0,25 (i.e. multiplied by 4) when computing the manufacturing impacts of this RU.</t>
   </si>
 </sst>
 </file>
@@ -1588,6 +1588,65 @@
     <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1606,65 +1665,6 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="2" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Excel Built-in Explanatory Text" xfId="3" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
@@ -1820,33 +1820,14 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Inventory - Manufacturing"/>
-      <sheetName val="Inventory - Use"/>
-      <sheetName val="LCA"/>
-      <sheetName val="LCIA"/>
-      <sheetName val="Cost - Price"/>
-      <sheetName val="Staircase"/>
-      <sheetName val="Faults &amp; Prev. Maint."/>
-      <sheetName val="Cur. Maint. (replac. matrix)"/>
-      <sheetName val="License (GNU LGPL)"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="1">
-          <cell r="B1" t="str">
-            <v>Example</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
+      <sheetData sheetId="0" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2029,1669 +2010,1669 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A194F3D1-0EB9-8C41-BB7E-1EE1EF91469E}">
   <dimension ref="A1:H187"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B2" s="102"/>
-      <c r="C2" s="101"/>
-      <c r="D2" s="101"/>
-      <c r="E2" s="101"/>
-      <c r="F2" s="101"/>
-      <c r="G2" s="101"/>
-      <c r="H2" s="100"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B3" s="99"/>
-      <c r="C3" s="98"/>
-      <c r="D3" s="98"/>
-      <c r="E3" s="98"/>
-      <c r="F3" s="98"/>
-      <c r="G3" s="98"/>
-      <c r="H3" s="97"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B4" s="99"/>
-      <c r="C4" s="98"/>
-      <c r="D4" s="98"/>
-      <c r="E4" s="98"/>
-      <c r="F4" s="98"/>
-      <c r="G4" s="98"/>
-      <c r="H4" s="97"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B5" s="99"/>
-      <c r="C5" s="98"/>
-      <c r="D5" s="98"/>
-      <c r="E5" s="98"/>
-      <c r="F5" s="98"/>
-      <c r="G5" s="98"/>
-      <c r="H5" s="97"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B6" s="99"/>
-      <c r="C6" s="98"/>
-      <c r="D6" s="98"/>
-      <c r="E6" s="98"/>
-      <c r="F6" s="98"/>
-      <c r="G6" s="98"/>
-      <c r="H6" s="97"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B7" s="99"/>
-      <c r="C7" s="98"/>
-      <c r="D7" s="98"/>
-      <c r="E7" s="98"/>
-      <c r="F7" s="98"/>
-      <c r="G7" s="98"/>
-      <c r="H7" s="97"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B8" s="99"/>
-      <c r="C8" s="98"/>
-      <c r="D8" s="98"/>
-      <c r="E8" s="98"/>
-      <c r="F8" s="98"/>
-      <c r="G8" s="98"/>
-      <c r="H8" s="97"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B9" s="99"/>
-      <c r="C9" s="98"/>
-      <c r="D9" s="98"/>
-      <c r="E9" s="98"/>
-      <c r="F9" s="98"/>
-      <c r="G9" s="98"/>
-      <c r="H9" s="97"/>
-    </row>
-    <row r="10" spans="1:8" ht="20" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="96"/>
-      <c r="C10" s="95"/>
-      <c r="D10" s="95"/>
-      <c r="E10" s="95"/>
-      <c r="F10" s="95"/>
-      <c r="G10" s="94" t="s">
-        <v>237</v>
-      </c>
-      <c r="H10" s="93" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B2" s="84"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="83"/>
+      <c r="F2" s="83"/>
+      <c r="G2" s="83"/>
+      <c r="H2" s="82"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B3" s="81"/>
+      <c r="C3" s="80"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="79"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B4" s="81"/>
+      <c r="C4" s="80"/>
+      <c r="D4" s="80"/>
+      <c r="E4" s="80"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="80"/>
+      <c r="H4" s="79"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B5" s="81"/>
+      <c r="C5" s="80"/>
+      <c r="D5" s="80"/>
+      <c r="E5" s="80"/>
+      <c r="F5" s="80"/>
+      <c r="G5" s="80"/>
+      <c r="H5" s="79"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B6" s="81"/>
+      <c r="C6" s="80"/>
+      <c r="D6" s="80"/>
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80"/>
+      <c r="H6" s="79"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B7" s="81"/>
+      <c r="C7" s="80"/>
+      <c r="D7" s="80"/>
+      <c r="E7" s="80"/>
+      <c r="F7" s="80"/>
+      <c r="G7" s="80"/>
+      <c r="H7" s="79"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B8" s="81"/>
+      <c r="C8" s="80"/>
+      <c r="D8" s="80"/>
+      <c r="E8" s="80"/>
+      <c r="F8" s="80"/>
+      <c r="G8" s="80"/>
+      <c r="H8" s="79"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B9" s="81"/>
+      <c r="C9" s="80"/>
+      <c r="D9" s="80"/>
+      <c r="E9" s="80"/>
+      <c r="F9" s="80"/>
+      <c r="G9" s="80"/>
+      <c r="H9" s="79"/>
+    </row>
+    <row r="10" spans="1:8" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B10" s="78"/>
+      <c r="C10" s="77"/>
+      <c r="D10" s="77"/>
+      <c r="E10" s="77"/>
+      <c r="F10" s="77"/>
+      <c r="G10" s="76" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="F11" s="92" t="s">
+      <c r="H10" s="75" t="s">
         <v>235</v>
       </c>
-      <c r="G11" s="91"/>
-      <c r="H11" s="91"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B12" s="90" t="s">
+    </row>
+    <row r="11" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F11" s="74" t="s">
         <v>234</v>
       </c>
-      <c r="C12" s="89"/>
-      <c r="D12" s="89"/>
-      <c r="E12" s="89"/>
-      <c r="F12" s="89"/>
-      <c r="G12" s="89"/>
-      <c r="H12" s="88"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B13" s="84"/>
-      <c r="H13" s="83"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B14" s="87"/>
-      <c r="C14" s="85" t="s">
+      <c r="G11" s="73"/>
+      <c r="H11" s="73"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B12" s="85" t="s">
         <v>233</v>
       </c>
-      <c r="H14" s="83"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B15" s="84"/>
-      <c r="H15" s="83"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B16" s="86"/>
-      <c r="C16" s="85" t="s">
+      <c r="C12" s="86"/>
+      <c r="D12" s="86"/>
+      <c r="E12" s="86"/>
+      <c r="F12" s="86"/>
+      <c r="G12" s="86"/>
+      <c r="H12" s="87"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B13" s="69"/>
+      <c r="H13" s="68"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B14" s="72"/>
+      <c r="C14" s="70" t="s">
         <v>232</v>
       </c>
-      <c r="H16" s="83"/>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B17" s="84"/>
-      <c r="H17" s="83"/>
-    </row>
-    <row r="18" spans="2:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="82" t="s">
+      <c r="H14" s="68"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B15" s="69"/>
+      <c r="H15" s="68"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B16" s="71"/>
+      <c r="C16" s="70" t="s">
         <v>231</v>
       </c>
-      <c r="C18" s="81" t="s">
+      <c r="H16" s="68"/>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B17" s="69"/>
+      <c r="H17" s="68"/>
+    </row>
+    <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B18" s="67" t="s">
         <v>230</v>
       </c>
-      <c r="D18" s="80"/>
-      <c r="E18" s="80"/>
-      <c r="F18" s="80"/>
-      <c r="G18" s="80"/>
-      <c r="H18" s="79"/>
-    </row>
-    <row r="19" spans="2:8" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="78" t="s">
+      <c r="C18" s="66" t="s">
         <v>229</v>
       </c>
-      <c r="C20" s="77"/>
-      <c r="D20" s="77"/>
-      <c r="E20" s="77"/>
-      <c r="F20" s="77"/>
-      <c r="G20" s="77"/>
-      <c r="H20" s="76"/>
-    </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B21" s="75"/>
-      <c r="C21" s="74"/>
-      <c r="D21" s="74"/>
-      <c r="E21" s="74"/>
-      <c r="F21" s="74"/>
-      <c r="G21" s="74"/>
-      <c r="H21" s="73"/>
-    </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B22" s="75"/>
-      <c r="C22" s="74"/>
-      <c r="D22" s="74"/>
-      <c r="E22" s="74"/>
-      <c r="F22" s="74"/>
-      <c r="G22" s="74"/>
-      <c r="H22" s="73"/>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B23" s="75"/>
-      <c r="C23" s="74"/>
-      <c r="D23" s="74"/>
-      <c r="E23" s="74"/>
-      <c r="F23" s="74"/>
-      <c r="G23" s="74"/>
-      <c r="H23" s="73"/>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B24" s="75"/>
-      <c r="C24" s="74"/>
-      <c r="D24" s="74"/>
-      <c r="E24" s="74"/>
-      <c r="F24" s="74"/>
-      <c r="G24" s="74"/>
-      <c r="H24" s="73"/>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B25" s="75"/>
-      <c r="C25" s="74"/>
-      <c r="D25" s="74"/>
-      <c r="E25" s="74"/>
-      <c r="F25" s="74"/>
-      <c r="G25" s="74"/>
-      <c r="H25" s="73"/>
-    </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B26" s="75"/>
-      <c r="C26" s="74"/>
-      <c r="D26" s="74"/>
-      <c r="E26" s="74"/>
-      <c r="F26" s="74"/>
-      <c r="G26" s="74"/>
-      <c r="H26" s="73"/>
-    </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B27" s="75"/>
-      <c r="C27" s="74"/>
-      <c r="D27" s="74"/>
-      <c r="E27" s="74"/>
-      <c r="F27" s="74"/>
-      <c r="G27" s="74"/>
-      <c r="H27" s="73"/>
-    </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B28" s="75"/>
-      <c r="C28" s="74"/>
-      <c r="D28" s="74"/>
-      <c r="E28" s="74"/>
-      <c r="F28" s="74"/>
-      <c r="G28" s="74"/>
-      <c r="H28" s="73"/>
-    </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B29" s="75"/>
-      <c r="C29" s="74"/>
-      <c r="D29" s="74"/>
-      <c r="E29" s="74"/>
-      <c r="F29" s="74"/>
-      <c r="G29" s="74"/>
-      <c r="H29" s="73"/>
-    </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B30" s="75"/>
-      <c r="C30" s="74"/>
-      <c r="D30" s="74"/>
-      <c r="E30" s="74"/>
-      <c r="F30" s="74"/>
-      <c r="G30" s="74"/>
-      <c r="H30" s="73"/>
-    </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B31" s="75"/>
-      <c r="C31" s="74"/>
-      <c r="D31" s="74"/>
-      <c r="E31" s="74"/>
-      <c r="F31" s="74"/>
-      <c r="G31" s="74"/>
-      <c r="H31" s="73"/>
-    </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B32" s="75"/>
-      <c r="C32" s="74"/>
-      <c r="D32" s="74"/>
-      <c r="E32" s="74"/>
-      <c r="F32" s="74"/>
-      <c r="G32" s="74"/>
-      <c r="H32" s="73"/>
-    </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="75"/>
-      <c r="C33" s="74"/>
-      <c r="D33" s="74"/>
-      <c r="E33" s="74"/>
-      <c r="F33" s="74"/>
-      <c r="G33" s="74"/>
-      <c r="H33" s="73"/>
-    </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B34" s="75"/>
-      <c r="C34" s="74"/>
-      <c r="D34" s="74"/>
-      <c r="E34" s="74"/>
-      <c r="F34" s="74"/>
-      <c r="G34" s="74"/>
-      <c r="H34" s="73"/>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B35" s="75"/>
-      <c r="C35" s="74"/>
-      <c r="D35" s="74"/>
-      <c r="E35" s="74"/>
-      <c r="F35" s="74"/>
-      <c r="G35" s="74"/>
-      <c r="H35" s="73"/>
-    </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B36" s="75"/>
-      <c r="C36" s="74"/>
-      <c r="D36" s="74"/>
-      <c r="E36" s="74"/>
-      <c r="F36" s="74"/>
-      <c r="G36" s="74"/>
-      <c r="H36" s="73"/>
-    </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B37" s="75"/>
-      <c r="C37" s="74"/>
-      <c r="D37" s="74"/>
-      <c r="E37" s="74"/>
-      <c r="F37" s="74"/>
-      <c r="G37" s="74"/>
-      <c r="H37" s="73"/>
-    </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B38" s="75"/>
-      <c r="C38" s="74"/>
-      <c r="D38" s="74"/>
-      <c r="E38" s="74"/>
-      <c r="F38" s="74"/>
-      <c r="G38" s="74"/>
-      <c r="H38" s="73"/>
-    </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B39" s="75"/>
-      <c r="C39" s="74"/>
-      <c r="D39" s="74"/>
-      <c r="E39" s="74"/>
-      <c r="F39" s="74"/>
-      <c r="G39" s="74"/>
-      <c r="H39" s="73"/>
-    </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B40" s="75"/>
-      <c r="C40" s="74"/>
-      <c r="D40" s="74"/>
-      <c r="E40" s="74"/>
-      <c r="F40" s="74"/>
-      <c r="G40" s="74"/>
-      <c r="H40" s="73"/>
-    </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B41" s="75"/>
-      <c r="C41" s="74"/>
-      <c r="D41" s="74"/>
-      <c r="E41" s="74"/>
-      <c r="F41" s="74"/>
-      <c r="G41" s="74"/>
-      <c r="H41" s="73"/>
-    </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="75"/>
-      <c r="C42" s="74"/>
-      <c r="D42" s="74"/>
-      <c r="E42" s="74"/>
-      <c r="F42" s="74"/>
-      <c r="G42" s="74"/>
-      <c r="H42" s="73"/>
-    </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B43" s="75"/>
-      <c r="C43" s="74"/>
-      <c r="D43" s="74"/>
-      <c r="E43" s="74"/>
-      <c r="F43" s="74"/>
-      <c r="G43" s="74"/>
-      <c r="H43" s="73"/>
-    </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B44" s="75"/>
-      <c r="C44" s="74"/>
-      <c r="D44" s="74"/>
-      <c r="E44" s="74"/>
-      <c r="F44" s="74"/>
-      <c r="G44" s="74"/>
-      <c r="H44" s="73"/>
-    </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B45" s="75"/>
-      <c r="C45" s="74"/>
-      <c r="D45" s="74"/>
-      <c r="E45" s="74"/>
-      <c r="F45" s="74"/>
-      <c r="G45" s="74"/>
-      <c r="H45" s="73"/>
-    </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B46" s="75"/>
-      <c r="C46" s="74"/>
-      <c r="D46" s="74"/>
-      <c r="E46" s="74"/>
-      <c r="F46" s="74"/>
-      <c r="G46" s="74"/>
-      <c r="H46" s="73"/>
-    </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B47" s="75"/>
-      <c r="C47" s="74"/>
-      <c r="D47" s="74"/>
-      <c r="E47" s="74"/>
-      <c r="F47" s="74"/>
-      <c r="G47" s="74"/>
-      <c r="H47" s="73"/>
-    </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B48" s="75"/>
-      <c r="C48" s="74"/>
-      <c r="D48" s="74"/>
-      <c r="E48" s="74"/>
-      <c r="F48" s="74"/>
-      <c r="G48" s="74"/>
-      <c r="H48" s="73"/>
-    </row>
-    <row r="49" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B49" s="75"/>
-      <c r="C49" s="74"/>
-      <c r="D49" s="74"/>
-      <c r="E49" s="74"/>
-      <c r="F49" s="74"/>
-      <c r="G49" s="74"/>
-      <c r="H49" s="73"/>
-    </row>
-    <row r="50" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B50" s="75"/>
-      <c r="C50" s="74"/>
-      <c r="D50" s="74"/>
-      <c r="E50" s="74"/>
-      <c r="F50" s="74"/>
-      <c r="G50" s="74"/>
-      <c r="H50" s="73"/>
-    </row>
-    <row r="51" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B51" s="75"/>
-      <c r="C51" s="74"/>
-      <c r="D51" s="74"/>
-      <c r="E51" s="74"/>
-      <c r="F51" s="74"/>
-      <c r="G51" s="74"/>
-      <c r="H51" s="73"/>
-    </row>
-    <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="75"/>
-      <c r="C52" s="74"/>
-      <c r="D52" s="74"/>
-      <c r="E52" s="74"/>
-      <c r="F52" s="74"/>
-      <c r="G52" s="74"/>
-      <c r="H52" s="73"/>
-    </row>
-    <row r="53" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B53" s="75"/>
-      <c r="C53" s="74"/>
-      <c r="D53" s="74"/>
-      <c r="E53" s="74"/>
-      <c r="F53" s="74"/>
-      <c r="G53" s="74"/>
-      <c r="H53" s="73"/>
-    </row>
-    <row r="54" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B54" s="75"/>
-      <c r="C54" s="74"/>
-      <c r="D54" s="74"/>
-      <c r="E54" s="74"/>
-      <c r="F54" s="74"/>
-      <c r="G54" s="74"/>
-      <c r="H54" s="73"/>
-    </row>
-    <row r="55" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B55" s="75"/>
-      <c r="C55" s="74"/>
-      <c r="D55" s="74"/>
-      <c r="E55" s="74"/>
-      <c r="F55" s="74"/>
-      <c r="G55" s="74"/>
-      <c r="H55" s="73"/>
-    </row>
-    <row r="56" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B56" s="75"/>
-      <c r="C56" s="74"/>
-      <c r="D56" s="74"/>
-      <c r="E56" s="74"/>
-      <c r="F56" s="74"/>
-      <c r="G56" s="74"/>
-      <c r="H56" s="73"/>
-    </row>
-    <row r="57" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B57" s="75"/>
-      <c r="C57" s="74"/>
-      <c r="D57" s="74"/>
-      <c r="E57" s="74"/>
-      <c r="F57" s="74"/>
-      <c r="G57" s="74"/>
-      <c r="H57" s="73"/>
-    </row>
-    <row r="58" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B58" s="75"/>
-      <c r="C58" s="74"/>
-      <c r="D58" s="74"/>
-      <c r="E58" s="74"/>
-      <c r="F58" s="74"/>
-      <c r="G58" s="74"/>
-      <c r="H58" s="73"/>
-    </row>
-    <row r="59" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B59" s="75"/>
-      <c r="C59" s="74"/>
-      <c r="D59" s="74"/>
-      <c r="E59" s="74"/>
-      <c r="F59" s="74"/>
-      <c r="G59" s="74"/>
-      <c r="H59" s="73"/>
-    </row>
-    <row r="60" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B60" s="75"/>
-      <c r="C60" s="74"/>
-      <c r="D60" s="74"/>
-      <c r="E60" s="74"/>
-      <c r="F60" s="74"/>
-      <c r="G60" s="74"/>
-      <c r="H60" s="73"/>
-    </row>
-    <row r="61" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B61" s="75"/>
-      <c r="C61" s="74"/>
-      <c r="D61" s="74"/>
-      <c r="E61" s="74"/>
-      <c r="F61" s="74"/>
-      <c r="G61" s="74"/>
-      <c r="H61" s="73"/>
-    </row>
-    <row r="62" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B62" s="75"/>
-      <c r="C62" s="74"/>
-      <c r="D62" s="74"/>
-      <c r="E62" s="74"/>
-      <c r="F62" s="74"/>
-      <c r="G62" s="74"/>
-      <c r="H62" s="73"/>
-    </row>
-    <row r="63" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B63" s="75"/>
-      <c r="C63" s="74"/>
-      <c r="D63" s="74"/>
-      <c r="E63" s="74"/>
-      <c r="F63" s="74"/>
-      <c r="G63" s="74"/>
-      <c r="H63" s="73"/>
-    </row>
-    <row r="64" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B64" s="75"/>
-      <c r="C64" s="74"/>
-      <c r="D64" s="74"/>
-      <c r="E64" s="74"/>
-      <c r="F64" s="74"/>
-      <c r="G64" s="74"/>
-      <c r="H64" s="73"/>
-    </row>
-    <row r="65" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B65" s="75"/>
-      <c r="C65" s="74"/>
-      <c r="D65" s="74"/>
-      <c r="E65" s="74"/>
-      <c r="F65" s="74"/>
-      <c r="G65" s="74"/>
-      <c r="H65" s="73"/>
-    </row>
-    <row r="66" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B66" s="75"/>
-      <c r="C66" s="74"/>
-      <c r="D66" s="74"/>
-      <c r="E66" s="74"/>
-      <c r="F66" s="74"/>
-      <c r="G66" s="74"/>
-      <c r="H66" s="73"/>
-    </row>
-    <row r="67" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B67" s="75"/>
-      <c r="C67" s="74"/>
-      <c r="D67" s="74"/>
-      <c r="E67" s="74"/>
-      <c r="F67" s="74"/>
-      <c r="G67" s="74"/>
-      <c r="H67" s="73"/>
-    </row>
-    <row r="68" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B68" s="75"/>
-      <c r="C68" s="74"/>
-      <c r="D68" s="74"/>
-      <c r="E68" s="74"/>
-      <c r="F68" s="74"/>
-      <c r="G68" s="74"/>
-      <c r="H68" s="73"/>
-    </row>
-    <row r="69" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B69" s="75"/>
-      <c r="C69" s="74"/>
-      <c r="D69" s="74"/>
-      <c r="E69" s="74"/>
-      <c r="F69" s="74"/>
-      <c r="G69" s="74"/>
-      <c r="H69" s="73"/>
-    </row>
-    <row r="70" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B70" s="75"/>
-      <c r="C70" s="74"/>
-      <c r="D70" s="74"/>
-      <c r="E70" s="74"/>
-      <c r="F70" s="74"/>
-      <c r="G70" s="74"/>
-      <c r="H70" s="73"/>
-    </row>
-    <row r="71" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B71" s="75"/>
-      <c r="C71" s="74"/>
-      <c r="D71" s="74"/>
-      <c r="E71" s="74"/>
-      <c r="F71" s="74"/>
-      <c r="G71" s="74"/>
-      <c r="H71" s="73"/>
-    </row>
-    <row r="72" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B72" s="75"/>
-      <c r="C72" s="74"/>
-      <c r="D72" s="74"/>
-      <c r="E72" s="74"/>
-      <c r="F72" s="74"/>
-      <c r="G72" s="74"/>
-      <c r="H72" s="73"/>
-    </row>
-    <row r="73" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B73" s="75"/>
-      <c r="C73" s="74"/>
-      <c r="D73" s="74"/>
-      <c r="E73" s="74"/>
-      <c r="F73" s="74"/>
-      <c r="G73" s="74"/>
-      <c r="H73" s="73"/>
-    </row>
-    <row r="74" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B74" s="75"/>
-      <c r="C74" s="74"/>
-      <c r="D74" s="74"/>
-      <c r="E74" s="74"/>
-      <c r="F74" s="74"/>
-      <c r="G74" s="74"/>
-      <c r="H74" s="73"/>
-    </row>
-    <row r="75" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B75" s="75"/>
-      <c r="C75" s="74"/>
-      <c r="D75" s="74"/>
-      <c r="E75" s="74"/>
-      <c r="F75" s="74"/>
-      <c r="G75" s="74"/>
-      <c r="H75" s="73"/>
-    </row>
-    <row r="76" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B76" s="75"/>
-      <c r="C76" s="74"/>
-      <c r="D76" s="74"/>
-      <c r="E76" s="74"/>
-      <c r="F76" s="74"/>
-      <c r="G76" s="74"/>
-      <c r="H76" s="73"/>
-    </row>
-    <row r="77" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B77" s="75"/>
-      <c r="C77" s="74"/>
-      <c r="D77" s="74"/>
-      <c r="E77" s="74"/>
-      <c r="F77" s="74"/>
-      <c r="G77" s="74"/>
-      <c r="H77" s="73"/>
-    </row>
-    <row r="78" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B78" s="75"/>
-      <c r="C78" s="74"/>
-      <c r="D78" s="74"/>
-      <c r="E78" s="74"/>
-      <c r="F78" s="74"/>
-      <c r="G78" s="74"/>
-      <c r="H78" s="73"/>
-    </row>
-    <row r="79" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B79" s="75"/>
-      <c r="C79" s="74"/>
-      <c r="D79" s="74"/>
-      <c r="E79" s="74"/>
-      <c r="F79" s="74"/>
-      <c r="G79" s="74"/>
-      <c r="H79" s="73"/>
-    </row>
-    <row r="80" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B80" s="75"/>
-      <c r="C80" s="74"/>
-      <c r="D80" s="74"/>
-      <c r="E80" s="74"/>
-      <c r="F80" s="74"/>
-      <c r="G80" s="74"/>
-      <c r="H80" s="73"/>
-    </row>
-    <row r="81" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B81" s="75"/>
-      <c r="C81" s="74"/>
-      <c r="D81" s="74"/>
-      <c r="E81" s="74"/>
-      <c r="F81" s="74"/>
-      <c r="G81" s="74"/>
-      <c r="H81" s="73"/>
-    </row>
-    <row r="82" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B82" s="75"/>
-      <c r="C82" s="74"/>
-      <c r="D82" s="74"/>
-      <c r="E82" s="74"/>
-      <c r="F82" s="74"/>
-      <c r="G82" s="74"/>
-      <c r="H82" s="73"/>
-    </row>
-    <row r="83" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B83" s="75"/>
-      <c r="C83" s="74"/>
-      <c r="D83" s="74"/>
-      <c r="E83" s="74"/>
-      <c r="F83" s="74"/>
-      <c r="G83" s="74"/>
-      <c r="H83" s="73"/>
-    </row>
-    <row r="84" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B84" s="75"/>
-      <c r="C84" s="74"/>
-      <c r="D84" s="74"/>
-      <c r="E84" s="74"/>
-      <c r="F84" s="74"/>
-      <c r="G84" s="74"/>
-      <c r="H84" s="73"/>
-    </row>
-    <row r="85" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B85" s="75"/>
-      <c r="C85" s="74"/>
-      <c r="D85" s="74"/>
-      <c r="E85" s="74"/>
-      <c r="F85" s="74"/>
-      <c r="G85" s="74"/>
-      <c r="H85" s="73"/>
-    </row>
-    <row r="86" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B86" s="75"/>
-      <c r="C86" s="74"/>
-      <c r="D86" s="74"/>
-      <c r="E86" s="74"/>
-      <c r="F86" s="74"/>
-      <c r="G86" s="74"/>
-      <c r="H86" s="73"/>
-    </row>
-    <row r="87" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B87" s="75"/>
-      <c r="C87" s="74"/>
-      <c r="D87" s="74"/>
-      <c r="E87" s="74"/>
-      <c r="F87" s="74"/>
-      <c r="G87" s="74"/>
-      <c r="H87" s="73"/>
-    </row>
-    <row r="88" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B88" s="75"/>
-      <c r="C88" s="74"/>
-      <c r="D88" s="74"/>
-      <c r="E88" s="74"/>
-      <c r="F88" s="74"/>
-      <c r="G88" s="74"/>
-      <c r="H88" s="73"/>
-    </row>
-    <row r="89" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B89" s="75"/>
-      <c r="C89" s="74"/>
-      <c r="D89" s="74"/>
-      <c r="E89" s="74"/>
-      <c r="F89" s="74"/>
-      <c r="G89" s="74"/>
-      <c r="H89" s="73"/>
-    </row>
-    <row r="90" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B90" s="75"/>
-      <c r="C90" s="74"/>
-      <c r="D90" s="74"/>
-      <c r="E90" s="74"/>
-      <c r="F90" s="74"/>
-      <c r="G90" s="74"/>
-      <c r="H90" s="73"/>
-    </row>
-    <row r="91" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B91" s="75"/>
-      <c r="C91" s="74"/>
-      <c r="D91" s="74"/>
-      <c r="E91" s="74"/>
-      <c r="F91" s="74"/>
-      <c r="G91" s="74"/>
-      <c r="H91" s="73"/>
-    </row>
-    <row r="92" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B92" s="75"/>
-      <c r="C92" s="74"/>
-      <c r="D92" s="74"/>
-      <c r="E92" s="74"/>
-      <c r="F92" s="74"/>
-      <c r="G92" s="74"/>
-      <c r="H92" s="73"/>
-    </row>
-    <row r="93" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B93" s="75"/>
-      <c r="C93" s="74"/>
-      <c r="D93" s="74"/>
-      <c r="E93" s="74"/>
-      <c r="F93" s="74"/>
-      <c r="G93" s="74"/>
-      <c r="H93" s="73"/>
-    </row>
-    <row r="94" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B94" s="75"/>
-      <c r="C94" s="74"/>
-      <c r="D94" s="74"/>
-      <c r="E94" s="74"/>
-      <c r="F94" s="74"/>
-      <c r="G94" s="74"/>
-      <c r="H94" s="73"/>
-    </row>
-    <row r="95" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B95" s="75"/>
-      <c r="C95" s="74"/>
-      <c r="D95" s="74"/>
-      <c r="E95" s="74"/>
-      <c r="F95" s="74"/>
-      <c r="G95" s="74"/>
-      <c r="H95" s="73"/>
-    </row>
-    <row r="96" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B96" s="75"/>
-      <c r="C96" s="74"/>
-      <c r="D96" s="74"/>
-      <c r="E96" s="74"/>
-      <c r="F96" s="74"/>
-      <c r="G96" s="74"/>
-      <c r="H96" s="73"/>
-    </row>
-    <row r="97" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B97" s="75"/>
-      <c r="C97" s="74"/>
-      <c r="D97" s="74"/>
-      <c r="E97" s="74"/>
-      <c r="F97" s="74"/>
-      <c r="G97" s="74"/>
-      <c r="H97" s="73"/>
-    </row>
-    <row r="98" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B98" s="75"/>
-      <c r="C98" s="74"/>
-      <c r="D98" s="74"/>
-      <c r="E98" s="74"/>
-      <c r="F98" s="74"/>
-      <c r="G98" s="74"/>
-      <c r="H98" s="73"/>
-    </row>
-    <row r="99" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B99" s="75"/>
-      <c r="C99" s="74"/>
-      <c r="D99" s="74"/>
-      <c r="E99" s="74"/>
-      <c r="F99" s="74"/>
-      <c r="G99" s="74"/>
-      <c r="H99" s="73"/>
-    </row>
-    <row r="100" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B100" s="75"/>
-      <c r="C100" s="74"/>
-      <c r="D100" s="74"/>
-      <c r="E100" s="74"/>
-      <c r="F100" s="74"/>
-      <c r="G100" s="74"/>
-      <c r="H100" s="73"/>
-    </row>
-    <row r="101" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B101" s="75"/>
-      <c r="C101" s="74"/>
-      <c r="D101" s="74"/>
-      <c r="E101" s="74"/>
-      <c r="F101" s="74"/>
-      <c r="G101" s="74"/>
-      <c r="H101" s="73"/>
-    </row>
-    <row r="102" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B102" s="75"/>
-      <c r="C102" s="74"/>
-      <c r="D102" s="74"/>
-      <c r="E102" s="74"/>
-      <c r="F102" s="74"/>
-      <c r="G102" s="74"/>
-      <c r="H102" s="73"/>
-    </row>
-    <row r="103" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B103" s="75"/>
-      <c r="C103" s="74"/>
-      <c r="D103" s="74"/>
-      <c r="E103" s="74"/>
-      <c r="F103" s="74"/>
-      <c r="G103" s="74"/>
-      <c r="H103" s="73"/>
-    </row>
-    <row r="104" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B104" s="75"/>
-      <c r="C104" s="74"/>
-      <c r="D104" s="74"/>
-      <c r="E104" s="74"/>
-      <c r="F104" s="74"/>
-      <c r="G104" s="74"/>
-      <c r="H104" s="73"/>
-    </row>
-    <row r="105" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B105" s="75"/>
-      <c r="C105" s="74"/>
-      <c r="D105" s="74"/>
-      <c r="E105" s="74"/>
-      <c r="F105" s="74"/>
-      <c r="G105" s="74"/>
-      <c r="H105" s="73"/>
-    </row>
-    <row r="106" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B106" s="75"/>
-      <c r="C106" s="74"/>
-      <c r="D106" s="74"/>
-      <c r="E106" s="74"/>
-      <c r="F106" s="74"/>
-      <c r="G106" s="74"/>
-      <c r="H106" s="73"/>
-    </row>
-    <row r="107" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B107" s="75"/>
-      <c r="C107" s="74"/>
-      <c r="D107" s="74"/>
-      <c r="E107" s="74"/>
-      <c r="F107" s="74"/>
-      <c r="G107" s="74"/>
-      <c r="H107" s="73"/>
-    </row>
-    <row r="108" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B108" s="75"/>
-      <c r="C108" s="74"/>
-      <c r="D108" s="74"/>
-      <c r="E108" s="74"/>
-      <c r="F108" s="74"/>
-      <c r="G108" s="74"/>
-      <c r="H108" s="73"/>
-    </row>
-    <row r="109" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B109" s="75"/>
-      <c r="C109" s="74"/>
-      <c r="D109" s="74"/>
-      <c r="E109" s="74"/>
-      <c r="F109" s="74"/>
-      <c r="G109" s="74"/>
-      <c r="H109" s="73"/>
-    </row>
-    <row r="110" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B110" s="75"/>
-      <c r="C110" s="74"/>
-      <c r="D110" s="74"/>
-      <c r="E110" s="74"/>
-      <c r="F110" s="74"/>
-      <c r="G110" s="74"/>
-      <c r="H110" s="73"/>
-    </row>
-    <row r="111" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B111" s="75"/>
-      <c r="C111" s="74"/>
-      <c r="D111" s="74"/>
-      <c r="E111" s="74"/>
-      <c r="F111" s="74"/>
-      <c r="G111" s="74"/>
-      <c r="H111" s="73"/>
-    </row>
-    <row r="112" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B112" s="75"/>
-      <c r="C112" s="74"/>
-      <c r="D112" s="74"/>
-      <c r="E112" s="74"/>
-      <c r="F112" s="74"/>
-      <c r="G112" s="74"/>
-      <c r="H112" s="73"/>
-    </row>
-    <row r="113" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B113" s="75"/>
-      <c r="C113" s="74"/>
-      <c r="D113" s="74"/>
-      <c r="E113" s="74"/>
-      <c r="F113" s="74"/>
-      <c r="G113" s="74"/>
-      <c r="H113" s="73"/>
-    </row>
-    <row r="114" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B114" s="75"/>
-      <c r="C114" s="74"/>
-      <c r="D114" s="74"/>
-      <c r="E114" s="74"/>
-      <c r="F114" s="74"/>
-      <c r="G114" s="74"/>
-      <c r="H114" s="73"/>
-    </row>
-    <row r="115" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B115" s="75"/>
-      <c r="C115" s="74"/>
-      <c r="D115" s="74"/>
-      <c r="E115" s="74"/>
-      <c r="F115" s="74"/>
-      <c r="G115" s="74"/>
-      <c r="H115" s="73"/>
-    </row>
-    <row r="116" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B116" s="75"/>
-      <c r="C116" s="74"/>
-      <c r="D116" s="74"/>
-      <c r="E116" s="74"/>
-      <c r="F116" s="74"/>
-      <c r="G116" s="74"/>
-      <c r="H116" s="73"/>
-    </row>
-    <row r="117" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B117" s="75"/>
-      <c r="C117" s="74"/>
-      <c r="D117" s="74"/>
-      <c r="E117" s="74"/>
-      <c r="F117" s="74"/>
-      <c r="G117" s="74"/>
-      <c r="H117" s="73"/>
-    </row>
-    <row r="118" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B118" s="75"/>
-      <c r="C118" s="74"/>
-      <c r="D118" s="74"/>
-      <c r="E118" s="74"/>
-      <c r="F118" s="74"/>
-      <c r="G118" s="74"/>
-      <c r="H118" s="73"/>
-    </row>
-    <row r="119" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B119" s="75"/>
-      <c r="C119" s="74"/>
-      <c r="D119" s="74"/>
-      <c r="E119" s="74"/>
-      <c r="F119" s="74"/>
-      <c r="G119" s="74"/>
-      <c r="H119" s="73"/>
-    </row>
-    <row r="120" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B120" s="75"/>
-      <c r="C120" s="74"/>
-      <c r="D120" s="74"/>
-      <c r="E120" s="74"/>
-      <c r="F120" s="74"/>
-      <c r="G120" s="74"/>
-      <c r="H120" s="73"/>
-    </row>
-    <row r="121" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B121" s="75"/>
-      <c r="C121" s="74"/>
-      <c r="D121" s="74"/>
-      <c r="E121" s="74"/>
-      <c r="F121" s="74"/>
-      <c r="G121" s="74"/>
-      <c r="H121" s="73"/>
-    </row>
-    <row r="122" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B122" s="75"/>
-      <c r="C122" s="74"/>
-      <c r="D122" s="74"/>
-      <c r="E122" s="74"/>
-      <c r="F122" s="74"/>
-      <c r="G122" s="74"/>
-      <c r="H122" s="73"/>
-    </row>
-    <row r="123" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B123" s="75"/>
-      <c r="C123" s="74"/>
-      <c r="D123" s="74"/>
-      <c r="E123" s="74"/>
-      <c r="F123" s="74"/>
-      <c r="G123" s="74"/>
-      <c r="H123" s="73"/>
-    </row>
-    <row r="124" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B124" s="75"/>
-      <c r="C124" s="74"/>
-      <c r="D124" s="74"/>
-      <c r="E124" s="74"/>
-      <c r="F124" s="74"/>
-      <c r="G124" s="74"/>
-      <c r="H124" s="73"/>
-    </row>
-    <row r="125" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B125" s="75"/>
-      <c r="C125" s="74"/>
-      <c r="D125" s="74"/>
-      <c r="E125" s="74"/>
-      <c r="F125" s="74"/>
-      <c r="G125" s="74"/>
-      <c r="H125" s="73"/>
-    </row>
-    <row r="126" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B126" s="75"/>
-      <c r="C126" s="74"/>
-      <c r="D126" s="74"/>
-      <c r="E126" s="74"/>
-      <c r="F126" s="74"/>
-      <c r="G126" s="74"/>
-      <c r="H126" s="73"/>
-    </row>
-    <row r="127" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B127" s="75"/>
-      <c r="C127" s="74"/>
-      <c r="D127" s="74"/>
-      <c r="E127" s="74"/>
-      <c r="F127" s="74"/>
-      <c r="G127" s="74"/>
-      <c r="H127" s="73"/>
-    </row>
-    <row r="128" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B128" s="75"/>
-      <c r="C128" s="74"/>
-      <c r="D128" s="74"/>
-      <c r="E128" s="74"/>
-      <c r="F128" s="74"/>
-      <c r="G128" s="74"/>
-      <c r="H128" s="73"/>
-    </row>
-    <row r="129" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B129" s="75"/>
-      <c r="C129" s="74"/>
-      <c r="D129" s="74"/>
-      <c r="E129" s="74"/>
-      <c r="F129" s="74"/>
-      <c r="G129" s="74"/>
-      <c r="H129" s="73"/>
-    </row>
-    <row r="130" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B130" s="75"/>
-      <c r="C130" s="74"/>
-      <c r="D130" s="74"/>
-      <c r="E130" s="74"/>
-      <c r="F130" s="74"/>
-      <c r="G130" s="74"/>
-      <c r="H130" s="73"/>
-    </row>
-    <row r="131" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B131" s="75"/>
-      <c r="C131" s="74"/>
-      <c r="D131" s="74"/>
-      <c r="E131" s="74"/>
-      <c r="F131" s="74"/>
-      <c r="G131" s="74"/>
-      <c r="H131" s="73"/>
-    </row>
-    <row r="132" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B132" s="75"/>
-      <c r="C132" s="74"/>
-      <c r="D132" s="74"/>
-      <c r="E132" s="74"/>
-      <c r="F132" s="74"/>
-      <c r="G132" s="74"/>
-      <c r="H132" s="73"/>
-    </row>
-    <row r="133" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B133" s="75"/>
-      <c r="C133" s="74"/>
-      <c r="D133" s="74"/>
-      <c r="E133" s="74"/>
-      <c r="F133" s="74"/>
-      <c r="G133" s="74"/>
-      <c r="H133" s="73"/>
-    </row>
-    <row r="134" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B134" s="75"/>
-      <c r="C134" s="74"/>
-      <c r="D134" s="74"/>
-      <c r="E134" s="74"/>
-      <c r="F134" s="74"/>
-      <c r="G134" s="74"/>
-      <c r="H134" s="73"/>
-    </row>
-    <row r="135" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B135" s="75"/>
-      <c r="C135" s="74"/>
-      <c r="D135" s="74"/>
-      <c r="E135" s="74"/>
-      <c r="F135" s="74"/>
-      <c r="G135" s="74"/>
-      <c r="H135" s="73"/>
-    </row>
-    <row r="136" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B136" s="75"/>
-      <c r="C136" s="74"/>
-      <c r="D136" s="74"/>
-      <c r="E136" s="74"/>
-      <c r="F136" s="74"/>
-      <c r="G136" s="74"/>
-      <c r="H136" s="73"/>
-    </row>
-    <row r="137" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B137" s="75"/>
-      <c r="C137" s="74"/>
-      <c r="D137" s="74"/>
-      <c r="E137" s="74"/>
-      <c r="F137" s="74"/>
-      <c r="G137" s="74"/>
-      <c r="H137" s="73"/>
-    </row>
-    <row r="138" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B138" s="75"/>
-      <c r="C138" s="74"/>
-      <c r="D138" s="74"/>
-      <c r="E138" s="74"/>
-      <c r="F138" s="74"/>
-      <c r="G138" s="74"/>
-      <c r="H138" s="73"/>
-    </row>
-    <row r="139" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B139" s="75"/>
-      <c r="C139" s="74"/>
-      <c r="D139" s="74"/>
-      <c r="E139" s="74"/>
-      <c r="F139" s="74"/>
-      <c r="G139" s="74"/>
-      <c r="H139" s="73"/>
-    </row>
-    <row r="140" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B140" s="75"/>
-      <c r="C140" s="74"/>
-      <c r="D140" s="74"/>
-      <c r="E140" s="74"/>
-      <c r="F140" s="74"/>
-      <c r="G140" s="74"/>
-      <c r="H140" s="73"/>
-    </row>
-    <row r="141" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B141" s="75"/>
-      <c r="C141" s="74"/>
-      <c r="D141" s="74"/>
-      <c r="E141" s="74"/>
-      <c r="F141" s="74"/>
-      <c r="G141" s="74"/>
-      <c r="H141" s="73"/>
-    </row>
-    <row r="142" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B142" s="75"/>
-      <c r="C142" s="74"/>
-      <c r="D142" s="74"/>
-      <c r="E142" s="74"/>
-      <c r="F142" s="74"/>
-      <c r="G142" s="74"/>
-      <c r="H142" s="73"/>
-    </row>
-    <row r="143" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B143" s="75"/>
-      <c r="C143" s="74"/>
-      <c r="D143" s="74"/>
-      <c r="E143" s="74"/>
-      <c r="F143" s="74"/>
-      <c r="G143" s="74"/>
-      <c r="H143" s="73"/>
-    </row>
-    <row r="144" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B144" s="75"/>
-      <c r="C144" s="74"/>
-      <c r="D144" s="74"/>
-      <c r="E144" s="74"/>
-      <c r="F144" s="74"/>
-      <c r="G144" s="74"/>
-      <c r="H144" s="73"/>
-    </row>
-    <row r="145" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B145" s="75"/>
-      <c r="C145" s="74"/>
-      <c r="D145" s="74"/>
-      <c r="E145" s="74"/>
-      <c r="F145" s="74"/>
-      <c r="G145" s="74"/>
-      <c r="H145" s="73"/>
-    </row>
-    <row r="146" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B146" s="75"/>
-      <c r="C146" s="74"/>
-      <c r="D146" s="74"/>
-      <c r="E146" s="74"/>
-      <c r="F146" s="74"/>
-      <c r="G146" s="74"/>
-      <c r="H146" s="73"/>
-    </row>
-    <row r="147" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B147" s="75"/>
-      <c r="C147" s="74"/>
-      <c r="D147" s="74"/>
-      <c r="E147" s="74"/>
-      <c r="F147" s="74"/>
-      <c r="G147" s="74"/>
-      <c r="H147" s="73"/>
-    </row>
-    <row r="148" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B148" s="75"/>
-      <c r="C148" s="74"/>
-      <c r="D148" s="74"/>
-      <c r="E148" s="74"/>
-      <c r="F148" s="74"/>
-      <c r="G148" s="74"/>
-      <c r="H148" s="73"/>
-    </row>
-    <row r="149" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B149" s="75"/>
-      <c r="C149" s="74"/>
-      <c r="D149" s="74"/>
-      <c r="E149" s="74"/>
-      <c r="F149" s="74"/>
-      <c r="G149" s="74"/>
-      <c r="H149" s="73"/>
-    </row>
-    <row r="150" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B150" s="75"/>
-      <c r="C150" s="74"/>
-      <c r="D150" s="74"/>
-      <c r="E150" s="74"/>
-      <c r="F150" s="74"/>
-      <c r="G150" s="74"/>
-      <c r="H150" s="73"/>
-    </row>
-    <row r="151" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B151" s="75"/>
-      <c r="C151" s="74"/>
-      <c r="D151" s="74"/>
-      <c r="E151" s="74"/>
-      <c r="F151" s="74"/>
-      <c r="G151" s="74"/>
-      <c r="H151" s="73"/>
-    </row>
-    <row r="152" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B152" s="75"/>
-      <c r="C152" s="74"/>
-      <c r="D152" s="74"/>
-      <c r="E152" s="74"/>
-      <c r="F152" s="74"/>
-      <c r="G152" s="74"/>
-      <c r="H152" s="73"/>
-    </row>
-    <row r="153" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B153" s="75"/>
-      <c r="C153" s="74"/>
-      <c r="D153" s="74"/>
-      <c r="E153" s="74"/>
-      <c r="F153" s="74"/>
-      <c r="G153" s="74"/>
-      <c r="H153" s="73"/>
-    </row>
-    <row r="154" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B154" s="75"/>
-      <c r="C154" s="74"/>
-      <c r="D154" s="74"/>
-      <c r="E154" s="74"/>
-      <c r="F154" s="74"/>
-      <c r="G154" s="74"/>
-      <c r="H154" s="73"/>
-    </row>
-    <row r="155" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B155" s="75"/>
-      <c r="C155" s="74"/>
-      <c r="D155" s="74"/>
-      <c r="E155" s="74"/>
-      <c r="F155" s="74"/>
-      <c r="G155" s="74"/>
-      <c r="H155" s="73"/>
-    </row>
-    <row r="156" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B156" s="75"/>
-      <c r="C156" s="74"/>
-      <c r="D156" s="74"/>
-      <c r="E156" s="74"/>
-      <c r="F156" s="74"/>
-      <c r="G156" s="74"/>
-      <c r="H156" s="73"/>
-    </row>
-    <row r="157" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B157" s="75"/>
-      <c r="C157" s="74"/>
-      <c r="D157" s="74"/>
-      <c r="E157" s="74"/>
-      <c r="F157" s="74"/>
-      <c r="G157" s="74"/>
-      <c r="H157" s="73"/>
-    </row>
-    <row r="158" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B158" s="75"/>
-      <c r="C158" s="74"/>
-      <c r="D158" s="74"/>
-      <c r="E158" s="74"/>
-      <c r="F158" s="74"/>
-      <c r="G158" s="74"/>
-      <c r="H158" s="73"/>
-    </row>
-    <row r="159" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B159" s="75"/>
-      <c r="C159" s="74"/>
-      <c r="D159" s="74"/>
-      <c r="E159" s="74"/>
-      <c r="F159" s="74"/>
-      <c r="G159" s="74"/>
-      <c r="H159" s="73"/>
-    </row>
-    <row r="160" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B160" s="75"/>
-      <c r="C160" s="74"/>
-      <c r="D160" s="74"/>
-      <c r="E160" s="74"/>
-      <c r="F160" s="74"/>
-      <c r="G160" s="74"/>
-      <c r="H160" s="73"/>
-    </row>
-    <row r="161" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B161" s="75"/>
-      <c r="C161" s="74"/>
-      <c r="D161" s="74"/>
-      <c r="E161" s="74"/>
-      <c r="F161" s="74"/>
-      <c r="G161" s="74"/>
-      <c r="H161" s="73"/>
-    </row>
-    <row r="162" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B162" s="75"/>
-      <c r="C162" s="74"/>
-      <c r="D162" s="74"/>
-      <c r="E162" s="74"/>
-      <c r="F162" s="74"/>
-      <c r="G162" s="74"/>
-      <c r="H162" s="73"/>
-    </row>
-    <row r="163" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B163" s="75"/>
-      <c r="C163" s="74"/>
-      <c r="D163" s="74"/>
-      <c r="E163" s="74"/>
-      <c r="F163" s="74"/>
-      <c r="G163" s="74"/>
-      <c r="H163" s="73"/>
-    </row>
-    <row r="164" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B164" s="75"/>
-      <c r="C164" s="74"/>
-      <c r="D164" s="74"/>
-      <c r="E164" s="74"/>
-      <c r="F164" s="74"/>
-      <c r="G164" s="74"/>
-      <c r="H164" s="73"/>
-    </row>
-    <row r="165" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B165" s="75"/>
-      <c r="C165" s="74"/>
-      <c r="D165" s="74"/>
-      <c r="E165" s="74"/>
-      <c r="F165" s="74"/>
-      <c r="G165" s="74"/>
-      <c r="H165" s="73"/>
-    </row>
-    <row r="166" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B166" s="75"/>
-      <c r="C166" s="74"/>
-      <c r="D166" s="74"/>
-      <c r="E166" s="74"/>
-      <c r="F166" s="74"/>
-      <c r="G166" s="74"/>
-      <c r="H166" s="73"/>
-    </row>
-    <row r="167" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B167" s="75"/>
-      <c r="C167" s="74"/>
-      <c r="D167" s="74"/>
-      <c r="E167" s="74"/>
-      <c r="F167" s="74"/>
-      <c r="G167" s="74"/>
-      <c r="H167" s="73"/>
-    </row>
-    <row r="168" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B168" s="75"/>
-      <c r="C168" s="74"/>
-      <c r="D168" s="74"/>
-      <c r="E168" s="74"/>
-      <c r="F168" s="74"/>
-      <c r="G168" s="74"/>
-      <c r="H168" s="73"/>
-    </row>
-    <row r="169" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B169" s="75"/>
-      <c r="C169" s="74"/>
-      <c r="D169" s="74"/>
-      <c r="E169" s="74"/>
-      <c r="F169" s="74"/>
-      <c r="G169" s="74"/>
-      <c r="H169" s="73"/>
-    </row>
-    <row r="170" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B170" s="75"/>
-      <c r="C170" s="74"/>
-      <c r="D170" s="74"/>
-      <c r="E170" s="74"/>
-      <c r="F170" s="74"/>
-      <c r="G170" s="74"/>
-      <c r="H170" s="73"/>
-    </row>
-    <row r="171" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B171" s="75"/>
-      <c r="C171" s="74"/>
-      <c r="D171" s="74"/>
-      <c r="E171" s="74"/>
-      <c r="F171" s="74"/>
-      <c r="G171" s="74"/>
-      <c r="H171" s="73"/>
-    </row>
-    <row r="172" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B172" s="75"/>
-      <c r="C172" s="74"/>
-      <c r="D172" s="74"/>
-      <c r="E172" s="74"/>
-      <c r="F172" s="74"/>
-      <c r="G172" s="74"/>
-      <c r="H172" s="73"/>
-    </row>
-    <row r="173" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B173" s="75"/>
-      <c r="C173" s="74"/>
-      <c r="D173" s="74"/>
-      <c r="E173" s="74"/>
-      <c r="F173" s="74"/>
-      <c r="G173" s="74"/>
-      <c r="H173" s="73"/>
-    </row>
-    <row r="174" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B174" s="75"/>
-      <c r="C174" s="74"/>
-      <c r="D174" s="74"/>
-      <c r="E174" s="74"/>
-      <c r="F174" s="74"/>
-      <c r="G174" s="74"/>
-      <c r="H174" s="73"/>
-    </row>
-    <row r="175" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B175" s="75"/>
-      <c r="C175" s="74"/>
-      <c r="D175" s="74"/>
-      <c r="E175" s="74"/>
-      <c r="F175" s="74"/>
-      <c r="G175" s="74"/>
-      <c r="H175" s="73"/>
-    </row>
-    <row r="176" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B176" s="75"/>
-      <c r="C176" s="74"/>
-      <c r="D176" s="74"/>
-      <c r="E176" s="74"/>
-      <c r="F176" s="74"/>
-      <c r="G176" s="74"/>
-      <c r="H176" s="73"/>
-    </row>
-    <row r="177" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B177" s="75"/>
-      <c r="C177" s="74"/>
-      <c r="D177" s="74"/>
-      <c r="E177" s="74"/>
-      <c r="F177" s="74"/>
-      <c r="G177" s="74"/>
-      <c r="H177" s="73"/>
-    </row>
-    <row r="178" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B178" s="75"/>
-      <c r="C178" s="74"/>
-      <c r="D178" s="74"/>
-      <c r="E178" s="74"/>
-      <c r="F178" s="74"/>
-      <c r="G178" s="74"/>
-      <c r="H178" s="73"/>
-    </row>
-    <row r="179" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B179" s="75"/>
-      <c r="C179" s="74"/>
-      <c r="D179" s="74"/>
-      <c r="E179" s="74"/>
-      <c r="F179" s="74"/>
-      <c r="G179" s="74"/>
-      <c r="H179" s="73"/>
-    </row>
-    <row r="180" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B180" s="75"/>
-      <c r="C180" s="74"/>
-      <c r="D180" s="74"/>
-      <c r="E180" s="74"/>
-      <c r="F180" s="74"/>
-      <c r="G180" s="74"/>
-      <c r="H180" s="73"/>
-    </row>
-    <row r="181" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B181" s="75"/>
-      <c r="C181" s="74"/>
-      <c r="D181" s="74"/>
-      <c r="E181" s="74"/>
-      <c r="F181" s="74"/>
-      <c r="G181" s="74"/>
-      <c r="H181" s="73"/>
-    </row>
-    <row r="182" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B182" s="75"/>
-      <c r="C182" s="74"/>
-      <c r="D182" s="74"/>
-      <c r="E182" s="74"/>
-      <c r="F182" s="74"/>
-      <c r="G182" s="74"/>
-      <c r="H182" s="73"/>
-    </row>
-    <row r="183" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B183" s="75"/>
-      <c r="C183" s="74"/>
-      <c r="D183" s="74"/>
-      <c r="E183" s="74"/>
-      <c r="F183" s="74"/>
-      <c r="G183" s="74"/>
-      <c r="H183" s="73"/>
-    </row>
-    <row r="184" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B184" s="75"/>
-      <c r="C184" s="74"/>
-      <c r="D184" s="74"/>
-      <c r="E184" s="74"/>
-      <c r="F184" s="74"/>
-      <c r="G184" s="74"/>
-      <c r="H184" s="73"/>
-    </row>
-    <row r="185" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B185" s="75"/>
-      <c r="C185" s="74"/>
-      <c r="D185" s="74"/>
-      <c r="E185" s="74"/>
-      <c r="F185" s="74"/>
-      <c r="G185" s="74"/>
-      <c r="H185" s="73"/>
-    </row>
-    <row r="186" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B186" s="75"/>
-      <c r="C186" s="74"/>
-      <c r="D186" s="74"/>
-      <c r="E186" s="74"/>
-      <c r="F186" s="74"/>
-      <c r="G186" s="74"/>
-      <c r="H186" s="73"/>
-    </row>
-    <row r="187" spans="2:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B187" s="72"/>
-      <c r="C187" s="71"/>
-      <c r="D187" s="71"/>
-      <c r="E187" s="71"/>
-      <c r="F187" s="71"/>
-      <c r="G187" s="71"/>
-      <c r="H187" s="70"/>
+      <c r="D18" s="65"/>
+      <c r="E18" s="65"/>
+      <c r="F18" s="65"/>
+      <c r="G18" s="65"/>
+      <c r="H18" s="64"/>
+    </row>
+    <row r="19" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="88" t="s">
+        <v>228</v>
+      </c>
+      <c r="C20" s="89"/>
+      <c r="D20" s="89"/>
+      <c r="E20" s="89"/>
+      <c r="F20" s="89"/>
+      <c r="G20" s="89"/>
+      <c r="H20" s="90"/>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B21" s="91"/>
+      <c r="C21" s="92"/>
+      <c r="D21" s="92"/>
+      <c r="E21" s="92"/>
+      <c r="F21" s="92"/>
+      <c r="G21" s="92"/>
+      <c r="H21" s="93"/>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B22" s="91"/>
+      <c r="C22" s="92"/>
+      <c r="D22" s="92"/>
+      <c r="E22" s="92"/>
+      <c r="F22" s="92"/>
+      <c r="G22" s="92"/>
+      <c r="H22" s="93"/>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B23" s="91"/>
+      <c r="C23" s="92"/>
+      <c r="D23" s="92"/>
+      <c r="E23" s="92"/>
+      <c r="F23" s="92"/>
+      <c r="G23" s="92"/>
+      <c r="H23" s="93"/>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B24" s="91"/>
+      <c r="C24" s="92"/>
+      <c r="D24" s="92"/>
+      <c r="E24" s="92"/>
+      <c r="F24" s="92"/>
+      <c r="G24" s="92"/>
+      <c r="H24" s="93"/>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B25" s="91"/>
+      <c r="C25" s="92"/>
+      <c r="D25" s="92"/>
+      <c r="E25" s="92"/>
+      <c r="F25" s="92"/>
+      <c r="G25" s="92"/>
+      <c r="H25" s="93"/>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B26" s="91"/>
+      <c r="C26" s="92"/>
+      <c r="D26" s="92"/>
+      <c r="E26" s="92"/>
+      <c r="F26" s="92"/>
+      <c r="G26" s="92"/>
+      <c r="H26" s="93"/>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B27" s="91"/>
+      <c r="C27" s="92"/>
+      <c r="D27" s="92"/>
+      <c r="E27" s="92"/>
+      <c r="F27" s="92"/>
+      <c r="G27" s="92"/>
+      <c r="H27" s="93"/>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B28" s="91"/>
+      <c r="C28" s="92"/>
+      <c r="D28" s="92"/>
+      <c r="E28" s="92"/>
+      <c r="F28" s="92"/>
+      <c r="G28" s="92"/>
+      <c r="H28" s="93"/>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B29" s="91"/>
+      <c r="C29" s="92"/>
+      <c r="D29" s="92"/>
+      <c r="E29" s="92"/>
+      <c r="F29" s="92"/>
+      <c r="G29" s="92"/>
+      <c r="H29" s="93"/>
+    </row>
+    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B30" s="91"/>
+      <c r="C30" s="92"/>
+      <c r="D30" s="92"/>
+      <c r="E30" s="92"/>
+      <c r="F30" s="92"/>
+      <c r="G30" s="92"/>
+      <c r="H30" s="93"/>
+    </row>
+    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B31" s="91"/>
+      <c r="C31" s="92"/>
+      <c r="D31" s="92"/>
+      <c r="E31" s="92"/>
+      <c r="F31" s="92"/>
+      <c r="G31" s="92"/>
+      <c r="H31" s="93"/>
+    </row>
+    <row r="32" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B32" s="91"/>
+      <c r="C32" s="92"/>
+      <c r="D32" s="92"/>
+      <c r="E32" s="92"/>
+      <c r="F32" s="92"/>
+      <c r="G32" s="92"/>
+      <c r="H32" s="93"/>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B33" s="91"/>
+      <c r="C33" s="92"/>
+      <c r="D33" s="92"/>
+      <c r="E33" s="92"/>
+      <c r="F33" s="92"/>
+      <c r="G33" s="92"/>
+      <c r="H33" s="93"/>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B34" s="91"/>
+      <c r="C34" s="92"/>
+      <c r="D34" s="92"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="92"/>
+      <c r="G34" s="92"/>
+      <c r="H34" s="93"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B35" s="91"/>
+      <c r="C35" s="92"/>
+      <c r="D35" s="92"/>
+      <c r="E35" s="92"/>
+      <c r="F35" s="92"/>
+      <c r="G35" s="92"/>
+      <c r="H35" s="93"/>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B36" s="91"/>
+      <c r="C36" s="92"/>
+      <c r="D36" s="92"/>
+      <c r="E36" s="92"/>
+      <c r="F36" s="92"/>
+      <c r="G36" s="92"/>
+      <c r="H36" s="93"/>
+    </row>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B37" s="91"/>
+      <c r="C37" s="92"/>
+      <c r="D37" s="92"/>
+      <c r="E37" s="92"/>
+      <c r="F37" s="92"/>
+      <c r="G37" s="92"/>
+      <c r="H37" s="93"/>
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B38" s="91"/>
+      <c r="C38" s="92"/>
+      <c r="D38" s="92"/>
+      <c r="E38" s="92"/>
+      <c r="F38" s="92"/>
+      <c r="G38" s="92"/>
+      <c r="H38" s="93"/>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B39" s="91"/>
+      <c r="C39" s="92"/>
+      <c r="D39" s="92"/>
+      <c r="E39" s="92"/>
+      <c r="F39" s="92"/>
+      <c r="G39" s="92"/>
+      <c r="H39" s="93"/>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B40" s="91"/>
+      <c r="C40" s="92"/>
+      <c r="D40" s="92"/>
+      <c r="E40" s="92"/>
+      <c r="F40" s="92"/>
+      <c r="G40" s="92"/>
+      <c r="H40" s="93"/>
+    </row>
+    <row r="41" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B41" s="91"/>
+      <c r="C41" s="92"/>
+      <c r="D41" s="92"/>
+      <c r="E41" s="92"/>
+      <c r="F41" s="92"/>
+      <c r="G41" s="92"/>
+      <c r="H41" s="93"/>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B42" s="91"/>
+      <c r="C42" s="92"/>
+      <c r="D42" s="92"/>
+      <c r="E42" s="92"/>
+      <c r="F42" s="92"/>
+      <c r="G42" s="92"/>
+      <c r="H42" s="93"/>
+    </row>
+    <row r="43" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B43" s="91"/>
+      <c r="C43" s="92"/>
+      <c r="D43" s="92"/>
+      <c r="E43" s="92"/>
+      <c r="F43" s="92"/>
+      <c r="G43" s="92"/>
+      <c r="H43" s="93"/>
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B44" s="91"/>
+      <c r="C44" s="92"/>
+      <c r="D44" s="92"/>
+      <c r="E44" s="92"/>
+      <c r="F44" s="92"/>
+      <c r="G44" s="92"/>
+      <c r="H44" s="93"/>
+    </row>
+    <row r="45" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B45" s="91"/>
+      <c r="C45" s="92"/>
+      <c r="D45" s="92"/>
+      <c r="E45" s="92"/>
+      <c r="F45" s="92"/>
+      <c r="G45" s="92"/>
+      <c r="H45" s="93"/>
+    </row>
+    <row r="46" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B46" s="91"/>
+      <c r="C46" s="92"/>
+      <c r="D46" s="92"/>
+      <c r="E46" s="92"/>
+      <c r="F46" s="92"/>
+      <c r="G46" s="92"/>
+      <c r="H46" s="93"/>
+    </row>
+    <row r="47" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B47" s="91"/>
+      <c r="C47" s="92"/>
+      <c r="D47" s="92"/>
+      <c r="E47" s="92"/>
+      <c r="F47" s="92"/>
+      <c r="G47" s="92"/>
+      <c r="H47" s="93"/>
+    </row>
+    <row r="48" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B48" s="91"/>
+      <c r="C48" s="92"/>
+      <c r="D48" s="92"/>
+      <c r="E48" s="92"/>
+      <c r="F48" s="92"/>
+      <c r="G48" s="92"/>
+      <c r="H48" s="93"/>
+    </row>
+    <row r="49" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B49" s="91"/>
+      <c r="C49" s="92"/>
+      <c r="D49" s="92"/>
+      <c r="E49" s="92"/>
+      <c r="F49" s="92"/>
+      <c r="G49" s="92"/>
+      <c r="H49" s="93"/>
+    </row>
+    <row r="50" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B50" s="91"/>
+      <c r="C50" s="92"/>
+      <c r="D50" s="92"/>
+      <c r="E50" s="92"/>
+      <c r="F50" s="92"/>
+      <c r="G50" s="92"/>
+      <c r="H50" s="93"/>
+    </row>
+    <row r="51" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B51" s="91"/>
+      <c r="C51" s="92"/>
+      <c r="D51" s="92"/>
+      <c r="E51" s="92"/>
+      <c r="F51" s="92"/>
+      <c r="G51" s="92"/>
+      <c r="H51" s="93"/>
+    </row>
+    <row r="52" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B52" s="91"/>
+      <c r="C52" s="92"/>
+      <c r="D52" s="92"/>
+      <c r="E52" s="92"/>
+      <c r="F52" s="92"/>
+      <c r="G52" s="92"/>
+      <c r="H52" s="93"/>
+    </row>
+    <row r="53" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B53" s="91"/>
+      <c r="C53" s="92"/>
+      <c r="D53" s="92"/>
+      <c r="E53" s="92"/>
+      <c r="F53" s="92"/>
+      <c r="G53" s="92"/>
+      <c r="H53" s="93"/>
+    </row>
+    <row r="54" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B54" s="91"/>
+      <c r="C54" s="92"/>
+      <c r="D54" s="92"/>
+      <c r="E54" s="92"/>
+      <c r="F54" s="92"/>
+      <c r="G54" s="92"/>
+      <c r="H54" s="93"/>
+    </row>
+    <row r="55" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B55" s="91"/>
+      <c r="C55" s="92"/>
+      <c r="D55" s="92"/>
+      <c r="E55" s="92"/>
+      <c r="F55" s="92"/>
+      <c r="G55" s="92"/>
+      <c r="H55" s="93"/>
+    </row>
+    <row r="56" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B56" s="91"/>
+      <c r="C56" s="92"/>
+      <c r="D56" s="92"/>
+      <c r="E56" s="92"/>
+      <c r="F56" s="92"/>
+      <c r="G56" s="92"/>
+      <c r="H56" s="93"/>
+    </row>
+    <row r="57" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B57" s="91"/>
+      <c r="C57" s="92"/>
+      <c r="D57" s="92"/>
+      <c r="E57" s="92"/>
+      <c r="F57" s="92"/>
+      <c r="G57" s="92"/>
+      <c r="H57" s="93"/>
+    </row>
+    <row r="58" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B58" s="91"/>
+      <c r="C58" s="92"/>
+      <c r="D58" s="92"/>
+      <c r="E58" s="92"/>
+      <c r="F58" s="92"/>
+      <c r="G58" s="92"/>
+      <c r="H58" s="93"/>
+    </row>
+    <row r="59" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B59" s="91"/>
+      <c r="C59" s="92"/>
+      <c r="D59" s="92"/>
+      <c r="E59" s="92"/>
+      <c r="F59" s="92"/>
+      <c r="G59" s="92"/>
+      <c r="H59" s="93"/>
+    </row>
+    <row r="60" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B60" s="91"/>
+      <c r="C60" s="92"/>
+      <c r="D60" s="92"/>
+      <c r="E60" s="92"/>
+      <c r="F60" s="92"/>
+      <c r="G60" s="92"/>
+      <c r="H60" s="93"/>
+    </row>
+    <row r="61" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B61" s="91"/>
+      <c r="C61" s="92"/>
+      <c r="D61" s="92"/>
+      <c r="E61" s="92"/>
+      <c r="F61" s="92"/>
+      <c r="G61" s="92"/>
+      <c r="H61" s="93"/>
+    </row>
+    <row r="62" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B62" s="91"/>
+      <c r="C62" s="92"/>
+      <c r="D62" s="92"/>
+      <c r="E62" s="92"/>
+      <c r="F62" s="92"/>
+      <c r="G62" s="92"/>
+      <c r="H62" s="93"/>
+    </row>
+    <row r="63" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B63" s="91"/>
+      <c r="C63" s="92"/>
+      <c r="D63" s="92"/>
+      <c r="E63" s="92"/>
+      <c r="F63" s="92"/>
+      <c r="G63" s="92"/>
+      <c r="H63" s="93"/>
+    </row>
+    <row r="64" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B64" s="91"/>
+      <c r="C64" s="92"/>
+      <c r="D64" s="92"/>
+      <c r="E64" s="92"/>
+      <c r="F64" s="92"/>
+      <c r="G64" s="92"/>
+      <c r="H64" s="93"/>
+    </row>
+    <row r="65" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B65" s="91"/>
+      <c r="C65" s="92"/>
+      <c r="D65" s="92"/>
+      <c r="E65" s="92"/>
+      <c r="F65" s="92"/>
+      <c r="G65" s="92"/>
+      <c r="H65" s="93"/>
+    </row>
+    <row r="66" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B66" s="91"/>
+      <c r="C66" s="92"/>
+      <c r="D66" s="92"/>
+      <c r="E66" s="92"/>
+      <c r="F66" s="92"/>
+      <c r="G66" s="92"/>
+      <c r="H66" s="93"/>
+    </row>
+    <row r="67" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B67" s="91"/>
+      <c r="C67" s="92"/>
+      <c r="D67" s="92"/>
+      <c r="E67" s="92"/>
+      <c r="F67" s="92"/>
+      <c r="G67" s="92"/>
+      <c r="H67" s="93"/>
+    </row>
+    <row r="68" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B68" s="91"/>
+      <c r="C68" s="92"/>
+      <c r="D68" s="92"/>
+      <c r="E68" s="92"/>
+      <c r="F68" s="92"/>
+      <c r="G68" s="92"/>
+      <c r="H68" s="93"/>
+    </row>
+    <row r="69" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B69" s="91"/>
+      <c r="C69" s="92"/>
+      <c r="D69" s="92"/>
+      <c r="E69" s="92"/>
+      <c r="F69" s="92"/>
+      <c r="G69" s="92"/>
+      <c r="H69" s="93"/>
+    </row>
+    <row r="70" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B70" s="91"/>
+      <c r="C70" s="92"/>
+      <c r="D70" s="92"/>
+      <c r="E70" s="92"/>
+      <c r="F70" s="92"/>
+      <c r="G70" s="92"/>
+      <c r="H70" s="93"/>
+    </row>
+    <row r="71" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B71" s="91"/>
+      <c r="C71" s="92"/>
+      <c r="D71" s="92"/>
+      <c r="E71" s="92"/>
+      <c r="F71" s="92"/>
+      <c r="G71" s="92"/>
+      <c r="H71" s="93"/>
+    </row>
+    <row r="72" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B72" s="91"/>
+      <c r="C72" s="92"/>
+      <c r="D72" s="92"/>
+      <c r="E72" s="92"/>
+      <c r="F72" s="92"/>
+      <c r="G72" s="92"/>
+      <c r="H72" s="93"/>
+    </row>
+    <row r="73" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B73" s="91"/>
+      <c r="C73" s="92"/>
+      <c r="D73" s="92"/>
+      <c r="E73" s="92"/>
+      <c r="F73" s="92"/>
+      <c r="G73" s="92"/>
+      <c r="H73" s="93"/>
+    </row>
+    <row r="74" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B74" s="91"/>
+      <c r="C74" s="92"/>
+      <c r="D74" s="92"/>
+      <c r="E74" s="92"/>
+      <c r="F74" s="92"/>
+      <c r="G74" s="92"/>
+      <c r="H74" s="93"/>
+    </row>
+    <row r="75" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B75" s="91"/>
+      <c r="C75" s="92"/>
+      <c r="D75" s="92"/>
+      <c r="E75" s="92"/>
+      <c r="F75" s="92"/>
+      <c r="G75" s="92"/>
+      <c r="H75" s="93"/>
+    </row>
+    <row r="76" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B76" s="91"/>
+      <c r="C76" s="92"/>
+      <c r="D76" s="92"/>
+      <c r="E76" s="92"/>
+      <c r="F76" s="92"/>
+      <c r="G76" s="92"/>
+      <c r="H76" s="93"/>
+    </row>
+    <row r="77" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B77" s="91"/>
+      <c r="C77" s="92"/>
+      <c r="D77" s="92"/>
+      <c r="E77" s="92"/>
+      <c r="F77" s="92"/>
+      <c r="G77" s="92"/>
+      <c r="H77" s="93"/>
+    </row>
+    <row r="78" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B78" s="91"/>
+      <c r="C78" s="92"/>
+      <c r="D78" s="92"/>
+      <c r="E78" s="92"/>
+      <c r="F78" s="92"/>
+      <c r="G78" s="92"/>
+      <c r="H78" s="93"/>
+    </row>
+    <row r="79" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B79" s="91"/>
+      <c r="C79" s="92"/>
+      <c r="D79" s="92"/>
+      <c r="E79" s="92"/>
+      <c r="F79" s="92"/>
+      <c r="G79" s="92"/>
+      <c r="H79" s="93"/>
+    </row>
+    <row r="80" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B80" s="91"/>
+      <c r="C80" s="92"/>
+      <c r="D80" s="92"/>
+      <c r="E80" s="92"/>
+      <c r="F80" s="92"/>
+      <c r="G80" s="92"/>
+      <c r="H80" s="93"/>
+    </row>
+    <row r="81" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B81" s="91"/>
+      <c r="C81" s="92"/>
+      <c r="D81" s="92"/>
+      <c r="E81" s="92"/>
+      <c r="F81" s="92"/>
+      <c r="G81" s="92"/>
+      <c r="H81" s="93"/>
+    </row>
+    <row r="82" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B82" s="91"/>
+      <c r="C82" s="92"/>
+      <c r="D82" s="92"/>
+      <c r="E82" s="92"/>
+      <c r="F82" s="92"/>
+      <c r="G82" s="92"/>
+      <c r="H82" s="93"/>
+    </row>
+    <row r="83" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B83" s="91"/>
+      <c r="C83" s="92"/>
+      <c r="D83" s="92"/>
+      <c r="E83" s="92"/>
+      <c r="F83" s="92"/>
+      <c r="G83" s="92"/>
+      <c r="H83" s="93"/>
+    </row>
+    <row r="84" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B84" s="91"/>
+      <c r="C84" s="92"/>
+      <c r="D84" s="92"/>
+      <c r="E84" s="92"/>
+      <c r="F84" s="92"/>
+      <c r="G84" s="92"/>
+      <c r="H84" s="93"/>
+    </row>
+    <row r="85" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B85" s="91"/>
+      <c r="C85" s="92"/>
+      <c r="D85" s="92"/>
+      <c r="E85" s="92"/>
+      <c r="F85" s="92"/>
+      <c r="G85" s="92"/>
+      <c r="H85" s="93"/>
+    </row>
+    <row r="86" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B86" s="91"/>
+      <c r="C86" s="92"/>
+      <c r="D86" s="92"/>
+      <c r="E86" s="92"/>
+      <c r="F86" s="92"/>
+      <c r="G86" s="92"/>
+      <c r="H86" s="93"/>
+    </row>
+    <row r="87" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B87" s="91"/>
+      <c r="C87" s="92"/>
+      <c r="D87" s="92"/>
+      <c r="E87" s="92"/>
+      <c r="F87" s="92"/>
+      <c r="G87" s="92"/>
+      <c r="H87" s="93"/>
+    </row>
+    <row r="88" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B88" s="91"/>
+      <c r="C88" s="92"/>
+      <c r="D88" s="92"/>
+      <c r="E88" s="92"/>
+      <c r="F88" s="92"/>
+      <c r="G88" s="92"/>
+      <c r="H88" s="93"/>
+    </row>
+    <row r="89" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B89" s="91"/>
+      <c r="C89" s="92"/>
+      <c r="D89" s="92"/>
+      <c r="E89" s="92"/>
+      <c r="F89" s="92"/>
+      <c r="G89" s="92"/>
+      <c r="H89" s="93"/>
+    </row>
+    <row r="90" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B90" s="91"/>
+      <c r="C90" s="92"/>
+      <c r="D90" s="92"/>
+      <c r="E90" s="92"/>
+      <c r="F90" s="92"/>
+      <c r="G90" s="92"/>
+      <c r="H90" s="93"/>
+    </row>
+    <row r="91" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B91" s="91"/>
+      <c r="C91" s="92"/>
+      <c r="D91" s="92"/>
+      <c r="E91" s="92"/>
+      <c r="F91" s="92"/>
+      <c r="G91" s="92"/>
+      <c r="H91" s="93"/>
+    </row>
+    <row r="92" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B92" s="91"/>
+      <c r="C92" s="92"/>
+      <c r="D92" s="92"/>
+      <c r="E92" s="92"/>
+      <c r="F92" s="92"/>
+      <c r="G92" s="92"/>
+      <c r="H92" s="93"/>
+    </row>
+    <row r="93" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B93" s="91"/>
+      <c r="C93" s="92"/>
+      <c r="D93" s="92"/>
+      <c r="E93" s="92"/>
+      <c r="F93" s="92"/>
+      <c r="G93" s="92"/>
+      <c r="H93" s="93"/>
+    </row>
+    <row r="94" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B94" s="91"/>
+      <c r="C94" s="92"/>
+      <c r="D94" s="92"/>
+      <c r="E94" s="92"/>
+      <c r="F94" s="92"/>
+      <c r="G94" s="92"/>
+      <c r="H94" s="93"/>
+    </row>
+    <row r="95" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B95" s="91"/>
+      <c r="C95" s="92"/>
+      <c r="D95" s="92"/>
+      <c r="E95" s="92"/>
+      <c r="F95" s="92"/>
+      <c r="G95" s="92"/>
+      <c r="H95" s="93"/>
+    </row>
+    <row r="96" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B96" s="91"/>
+      <c r="C96" s="92"/>
+      <c r="D96" s="92"/>
+      <c r="E96" s="92"/>
+      <c r="F96" s="92"/>
+      <c r="G96" s="92"/>
+      <c r="H96" s="93"/>
+    </row>
+    <row r="97" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B97" s="91"/>
+      <c r="C97" s="92"/>
+      <c r="D97" s="92"/>
+      <c r="E97" s="92"/>
+      <c r="F97" s="92"/>
+      <c r="G97" s="92"/>
+      <c r="H97" s="93"/>
+    </row>
+    <row r="98" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B98" s="91"/>
+      <c r="C98" s="92"/>
+      <c r="D98" s="92"/>
+      <c r="E98" s="92"/>
+      <c r="F98" s="92"/>
+      <c r="G98" s="92"/>
+      <c r="H98" s="93"/>
+    </row>
+    <row r="99" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B99" s="91"/>
+      <c r="C99" s="92"/>
+      <c r="D99" s="92"/>
+      <c r="E99" s="92"/>
+      <c r="F99" s="92"/>
+      <c r="G99" s="92"/>
+      <c r="H99" s="93"/>
+    </row>
+    <row r="100" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B100" s="91"/>
+      <c r="C100" s="92"/>
+      <c r="D100" s="92"/>
+      <c r="E100" s="92"/>
+      <c r="F100" s="92"/>
+      <c r="G100" s="92"/>
+      <c r="H100" s="93"/>
+    </row>
+    <row r="101" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B101" s="91"/>
+      <c r="C101" s="92"/>
+      <c r="D101" s="92"/>
+      <c r="E101" s="92"/>
+      <c r="F101" s="92"/>
+      <c r="G101" s="92"/>
+      <c r="H101" s="93"/>
+    </row>
+    <row r="102" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B102" s="91"/>
+      <c r="C102" s="92"/>
+      <c r="D102" s="92"/>
+      <c r="E102" s="92"/>
+      <c r="F102" s="92"/>
+      <c r="G102" s="92"/>
+      <c r="H102" s="93"/>
+    </row>
+    <row r="103" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B103" s="91"/>
+      <c r="C103" s="92"/>
+      <c r="D103" s="92"/>
+      <c r="E103" s="92"/>
+      <c r="F103" s="92"/>
+      <c r="G103" s="92"/>
+      <c r="H103" s="93"/>
+    </row>
+    <row r="104" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B104" s="91"/>
+      <c r="C104" s="92"/>
+      <c r="D104" s="92"/>
+      <c r="E104" s="92"/>
+      <c r="F104" s="92"/>
+      <c r="G104" s="92"/>
+      <c r="H104" s="93"/>
+    </row>
+    <row r="105" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B105" s="91"/>
+      <c r="C105" s="92"/>
+      <c r="D105" s="92"/>
+      <c r="E105" s="92"/>
+      <c r="F105" s="92"/>
+      <c r="G105" s="92"/>
+      <c r="H105" s="93"/>
+    </row>
+    <row r="106" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B106" s="91"/>
+      <c r="C106" s="92"/>
+      <c r="D106" s="92"/>
+      <c r="E106" s="92"/>
+      <c r="F106" s="92"/>
+      <c r="G106" s="92"/>
+      <c r="H106" s="93"/>
+    </row>
+    <row r="107" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B107" s="91"/>
+      <c r="C107" s="92"/>
+      <c r="D107" s="92"/>
+      <c r="E107" s="92"/>
+      <c r="F107" s="92"/>
+      <c r="G107" s="92"/>
+      <c r="H107" s="93"/>
+    </row>
+    <row r="108" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B108" s="91"/>
+      <c r="C108" s="92"/>
+      <c r="D108" s="92"/>
+      <c r="E108" s="92"/>
+      <c r="F108" s="92"/>
+      <c r="G108" s="92"/>
+      <c r="H108" s="93"/>
+    </row>
+    <row r="109" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B109" s="91"/>
+      <c r="C109" s="92"/>
+      <c r="D109" s="92"/>
+      <c r="E109" s="92"/>
+      <c r="F109" s="92"/>
+      <c r="G109" s="92"/>
+      <c r="H109" s="93"/>
+    </row>
+    <row r="110" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B110" s="91"/>
+      <c r="C110" s="92"/>
+      <c r="D110" s="92"/>
+      <c r="E110" s="92"/>
+      <c r="F110" s="92"/>
+      <c r="G110" s="92"/>
+      <c r="H110" s="93"/>
+    </row>
+    <row r="111" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B111" s="91"/>
+      <c r="C111" s="92"/>
+      <c r="D111" s="92"/>
+      <c r="E111" s="92"/>
+      <c r="F111" s="92"/>
+      <c r="G111" s="92"/>
+      <c r="H111" s="93"/>
+    </row>
+    <row r="112" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B112" s="91"/>
+      <c r="C112" s="92"/>
+      <c r="D112" s="92"/>
+      <c r="E112" s="92"/>
+      <c r="F112" s="92"/>
+      <c r="G112" s="92"/>
+      <c r="H112" s="93"/>
+    </row>
+    <row r="113" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B113" s="91"/>
+      <c r="C113" s="92"/>
+      <c r="D113" s="92"/>
+      <c r="E113" s="92"/>
+      <c r="F113" s="92"/>
+      <c r="G113" s="92"/>
+      <c r="H113" s="93"/>
+    </row>
+    <row r="114" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B114" s="91"/>
+      <c r="C114" s="92"/>
+      <c r="D114" s="92"/>
+      <c r="E114" s="92"/>
+      <c r="F114" s="92"/>
+      <c r="G114" s="92"/>
+      <c r="H114" s="93"/>
+    </row>
+    <row r="115" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B115" s="91"/>
+      <c r="C115" s="92"/>
+      <c r="D115" s="92"/>
+      <c r="E115" s="92"/>
+      <c r="F115" s="92"/>
+      <c r="G115" s="92"/>
+      <c r="H115" s="93"/>
+    </row>
+    <row r="116" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B116" s="91"/>
+      <c r="C116" s="92"/>
+      <c r="D116" s="92"/>
+      <c r="E116" s="92"/>
+      <c r="F116" s="92"/>
+      <c r="G116" s="92"/>
+      <c r="H116" s="93"/>
+    </row>
+    <row r="117" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B117" s="91"/>
+      <c r="C117" s="92"/>
+      <c r="D117" s="92"/>
+      <c r="E117" s="92"/>
+      <c r="F117" s="92"/>
+      <c r="G117" s="92"/>
+      <c r="H117" s="93"/>
+    </row>
+    <row r="118" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B118" s="91"/>
+      <c r="C118" s="92"/>
+      <c r="D118" s="92"/>
+      <c r="E118" s="92"/>
+      <c r="F118" s="92"/>
+      <c r="G118" s="92"/>
+      <c r="H118" s="93"/>
+    </row>
+    <row r="119" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B119" s="91"/>
+      <c r="C119" s="92"/>
+      <c r="D119" s="92"/>
+      <c r="E119" s="92"/>
+      <c r="F119" s="92"/>
+      <c r="G119" s="92"/>
+      <c r="H119" s="93"/>
+    </row>
+    <row r="120" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B120" s="91"/>
+      <c r="C120" s="92"/>
+      <c r="D120" s="92"/>
+      <c r="E120" s="92"/>
+      <c r="F120" s="92"/>
+      <c r="G120" s="92"/>
+      <c r="H120" s="93"/>
+    </row>
+    <row r="121" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B121" s="91"/>
+      <c r="C121" s="92"/>
+      <c r="D121" s="92"/>
+      <c r="E121" s="92"/>
+      <c r="F121" s="92"/>
+      <c r="G121" s="92"/>
+      <c r="H121" s="93"/>
+    </row>
+    <row r="122" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B122" s="91"/>
+      <c r="C122" s="92"/>
+      <c r="D122" s="92"/>
+      <c r="E122" s="92"/>
+      <c r="F122" s="92"/>
+      <c r="G122" s="92"/>
+      <c r="H122" s="93"/>
+    </row>
+    <row r="123" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B123" s="91"/>
+      <c r="C123" s="92"/>
+      <c r="D123" s="92"/>
+      <c r="E123" s="92"/>
+      <c r="F123" s="92"/>
+      <c r="G123" s="92"/>
+      <c r="H123" s="93"/>
+    </row>
+    <row r="124" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B124" s="91"/>
+      <c r="C124" s="92"/>
+      <c r="D124" s="92"/>
+      <c r="E124" s="92"/>
+      <c r="F124" s="92"/>
+      <c r="G124" s="92"/>
+      <c r="H124" s="93"/>
+    </row>
+    <row r="125" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B125" s="91"/>
+      <c r="C125" s="92"/>
+      <c r="D125" s="92"/>
+      <c r="E125" s="92"/>
+      <c r="F125" s="92"/>
+      <c r="G125" s="92"/>
+      <c r="H125" s="93"/>
+    </row>
+    <row r="126" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B126" s="91"/>
+      <c r="C126" s="92"/>
+      <c r="D126" s="92"/>
+      <c r="E126" s="92"/>
+      <c r="F126" s="92"/>
+      <c r="G126" s="92"/>
+      <c r="H126" s="93"/>
+    </row>
+    <row r="127" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B127" s="91"/>
+      <c r="C127" s="92"/>
+      <c r="D127" s="92"/>
+      <c r="E127" s="92"/>
+      <c r="F127" s="92"/>
+      <c r="G127" s="92"/>
+      <c r="H127" s="93"/>
+    </row>
+    <row r="128" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B128" s="91"/>
+      <c r="C128" s="92"/>
+      <c r="D128" s="92"/>
+      <c r="E128" s="92"/>
+      <c r="F128" s="92"/>
+      <c r="G128" s="92"/>
+      <c r="H128" s="93"/>
+    </row>
+    <row r="129" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B129" s="91"/>
+      <c r="C129" s="92"/>
+      <c r="D129" s="92"/>
+      <c r="E129" s="92"/>
+      <c r="F129" s="92"/>
+      <c r="G129" s="92"/>
+      <c r="H129" s="93"/>
+    </row>
+    <row r="130" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B130" s="91"/>
+      <c r="C130" s="92"/>
+      <c r="D130" s="92"/>
+      <c r="E130" s="92"/>
+      <c r="F130" s="92"/>
+      <c r="G130" s="92"/>
+      <c r="H130" s="93"/>
+    </row>
+    <row r="131" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B131" s="91"/>
+      <c r="C131" s="92"/>
+      <c r="D131" s="92"/>
+      <c r="E131" s="92"/>
+      <c r="F131" s="92"/>
+      <c r="G131" s="92"/>
+      <c r="H131" s="93"/>
+    </row>
+    <row r="132" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B132" s="91"/>
+      <c r="C132" s="92"/>
+      <c r="D132" s="92"/>
+      <c r="E132" s="92"/>
+      <c r="F132" s="92"/>
+      <c r="G132" s="92"/>
+      <c r="H132" s="93"/>
+    </row>
+    <row r="133" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B133" s="91"/>
+      <c r="C133" s="92"/>
+      <c r="D133" s="92"/>
+      <c r="E133" s="92"/>
+      <c r="F133" s="92"/>
+      <c r="G133" s="92"/>
+      <c r="H133" s="93"/>
+    </row>
+    <row r="134" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B134" s="91"/>
+      <c r="C134" s="92"/>
+      <c r="D134" s="92"/>
+      <c r="E134" s="92"/>
+      <c r="F134" s="92"/>
+      <c r="G134" s="92"/>
+      <c r="H134" s="93"/>
+    </row>
+    <row r="135" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B135" s="91"/>
+      <c r="C135" s="92"/>
+      <c r="D135" s="92"/>
+      <c r="E135" s="92"/>
+      <c r="F135" s="92"/>
+      <c r="G135" s="92"/>
+      <c r="H135" s="93"/>
+    </row>
+    <row r="136" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B136" s="91"/>
+      <c r="C136" s="92"/>
+      <c r="D136" s="92"/>
+      <c r="E136" s="92"/>
+      <c r="F136" s="92"/>
+      <c r="G136" s="92"/>
+      <c r="H136" s="93"/>
+    </row>
+    <row r="137" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B137" s="91"/>
+      <c r="C137" s="92"/>
+      <c r="D137" s="92"/>
+      <c r="E137" s="92"/>
+      <c r="F137" s="92"/>
+      <c r="G137" s="92"/>
+      <c r="H137" s="93"/>
+    </row>
+    <row r="138" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B138" s="91"/>
+      <c r="C138" s="92"/>
+      <c r="D138" s="92"/>
+      <c r="E138" s="92"/>
+      <c r="F138" s="92"/>
+      <c r="G138" s="92"/>
+      <c r="H138" s="93"/>
+    </row>
+    <row r="139" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B139" s="91"/>
+      <c r="C139" s="92"/>
+      <c r="D139" s="92"/>
+      <c r="E139" s="92"/>
+      <c r="F139" s="92"/>
+      <c r="G139" s="92"/>
+      <c r="H139" s="93"/>
+    </row>
+    <row r="140" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B140" s="91"/>
+      <c r="C140" s="92"/>
+      <c r="D140" s="92"/>
+      <c r="E140" s="92"/>
+      <c r="F140" s="92"/>
+      <c r="G140" s="92"/>
+      <c r="H140" s="93"/>
+    </row>
+    <row r="141" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B141" s="91"/>
+      <c r="C141" s="92"/>
+      <c r="D141" s="92"/>
+      <c r="E141" s="92"/>
+      <c r="F141" s="92"/>
+      <c r="G141" s="92"/>
+      <c r="H141" s="93"/>
+    </row>
+    <row r="142" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B142" s="91"/>
+      <c r="C142" s="92"/>
+      <c r="D142" s="92"/>
+      <c r="E142" s="92"/>
+      <c r="F142" s="92"/>
+      <c r="G142" s="92"/>
+      <c r="H142" s="93"/>
+    </row>
+    <row r="143" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B143" s="91"/>
+      <c r="C143" s="92"/>
+      <c r="D143" s="92"/>
+      <c r="E143" s="92"/>
+      <c r="F143" s="92"/>
+      <c r="G143" s="92"/>
+      <c r="H143" s="93"/>
+    </row>
+    <row r="144" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B144" s="91"/>
+      <c r="C144" s="92"/>
+      <c r="D144" s="92"/>
+      <c r="E144" s="92"/>
+      <c r="F144" s="92"/>
+      <c r="G144" s="92"/>
+      <c r="H144" s="93"/>
+    </row>
+    <row r="145" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B145" s="91"/>
+      <c r="C145" s="92"/>
+      <c r="D145" s="92"/>
+      <c r="E145" s="92"/>
+      <c r="F145" s="92"/>
+      <c r="G145" s="92"/>
+      <c r="H145" s="93"/>
+    </row>
+    <row r="146" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B146" s="91"/>
+      <c r="C146" s="92"/>
+      <c r="D146" s="92"/>
+      <c r="E146" s="92"/>
+      <c r="F146" s="92"/>
+      <c r="G146" s="92"/>
+      <c r="H146" s="93"/>
+    </row>
+    <row r="147" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B147" s="91"/>
+      <c r="C147" s="92"/>
+      <c r="D147" s="92"/>
+      <c r="E147" s="92"/>
+      <c r="F147" s="92"/>
+      <c r="G147" s="92"/>
+      <c r="H147" s="93"/>
+    </row>
+    <row r="148" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B148" s="91"/>
+      <c r="C148" s="92"/>
+      <c r="D148" s="92"/>
+      <c r="E148" s="92"/>
+      <c r="F148" s="92"/>
+      <c r="G148" s="92"/>
+      <c r="H148" s="93"/>
+    </row>
+    <row r="149" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B149" s="91"/>
+      <c r="C149" s="92"/>
+      <c r="D149" s="92"/>
+      <c r="E149" s="92"/>
+      <c r="F149" s="92"/>
+      <c r="G149" s="92"/>
+      <c r="H149" s="93"/>
+    </row>
+    <row r="150" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B150" s="91"/>
+      <c r="C150" s="92"/>
+      <c r="D150" s="92"/>
+      <c r="E150" s="92"/>
+      <c r="F150" s="92"/>
+      <c r="G150" s="92"/>
+      <c r="H150" s="93"/>
+    </row>
+    <row r="151" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B151" s="91"/>
+      <c r="C151" s="92"/>
+      <c r="D151" s="92"/>
+      <c r="E151" s="92"/>
+      <c r="F151" s="92"/>
+      <c r="G151" s="92"/>
+      <c r="H151" s="93"/>
+    </row>
+    <row r="152" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B152" s="91"/>
+      <c r="C152" s="92"/>
+      <c r="D152" s="92"/>
+      <c r="E152" s="92"/>
+      <c r="F152" s="92"/>
+      <c r="G152" s="92"/>
+      <c r="H152" s="93"/>
+    </row>
+    <row r="153" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B153" s="91"/>
+      <c r="C153" s="92"/>
+      <c r="D153" s="92"/>
+      <c r="E153" s="92"/>
+      <c r="F153" s="92"/>
+      <c r="G153" s="92"/>
+      <c r="H153" s="93"/>
+    </row>
+    <row r="154" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B154" s="91"/>
+      <c r="C154" s="92"/>
+      <c r="D154" s="92"/>
+      <c r="E154" s="92"/>
+      <c r="F154" s="92"/>
+      <c r="G154" s="92"/>
+      <c r="H154" s="93"/>
+    </row>
+    <row r="155" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B155" s="91"/>
+      <c r="C155" s="92"/>
+      <c r="D155" s="92"/>
+      <c r="E155" s="92"/>
+      <c r="F155" s="92"/>
+      <c r="G155" s="92"/>
+      <c r="H155" s="93"/>
+    </row>
+    <row r="156" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B156" s="91"/>
+      <c r="C156" s="92"/>
+      <c r="D156" s="92"/>
+      <c r="E156" s="92"/>
+      <c r="F156" s="92"/>
+      <c r="G156" s="92"/>
+      <c r="H156" s="93"/>
+    </row>
+    <row r="157" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B157" s="91"/>
+      <c r="C157" s="92"/>
+      <c r="D157" s="92"/>
+      <c r="E157" s="92"/>
+      <c r="F157" s="92"/>
+      <c r="G157" s="92"/>
+      <c r="H157" s="93"/>
+    </row>
+    <row r="158" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B158" s="91"/>
+      <c r="C158" s="92"/>
+      <c r="D158" s="92"/>
+      <c r="E158" s="92"/>
+      <c r="F158" s="92"/>
+      <c r="G158" s="92"/>
+      <c r="H158" s="93"/>
+    </row>
+    <row r="159" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B159" s="91"/>
+      <c r="C159" s="92"/>
+      <c r="D159" s="92"/>
+      <c r="E159" s="92"/>
+      <c r="F159" s="92"/>
+      <c r="G159" s="92"/>
+      <c r="H159" s="93"/>
+    </row>
+    <row r="160" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B160" s="91"/>
+      <c r="C160" s="92"/>
+      <c r="D160" s="92"/>
+      <c r="E160" s="92"/>
+      <c r="F160" s="92"/>
+      <c r="G160" s="92"/>
+      <c r="H160" s="93"/>
+    </row>
+    <row r="161" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B161" s="91"/>
+      <c r="C161" s="92"/>
+      <c r="D161" s="92"/>
+      <c r="E161" s="92"/>
+      <c r="F161" s="92"/>
+      <c r="G161" s="92"/>
+      <c r="H161" s="93"/>
+    </row>
+    <row r="162" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B162" s="91"/>
+      <c r="C162" s="92"/>
+      <c r="D162" s="92"/>
+      <c r="E162" s="92"/>
+      <c r="F162" s="92"/>
+      <c r="G162" s="92"/>
+      <c r="H162" s="93"/>
+    </row>
+    <row r="163" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B163" s="91"/>
+      <c r="C163" s="92"/>
+      <c r="D163" s="92"/>
+      <c r="E163" s="92"/>
+      <c r="F163" s="92"/>
+      <c r="G163" s="92"/>
+      <c r="H163" s="93"/>
+    </row>
+    <row r="164" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B164" s="91"/>
+      <c r="C164" s="92"/>
+      <c r="D164" s="92"/>
+      <c r="E164" s="92"/>
+      <c r="F164" s="92"/>
+      <c r="G164" s="92"/>
+      <c r="H164" s="93"/>
+    </row>
+    <row r="165" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B165" s="91"/>
+      <c r="C165" s="92"/>
+      <c r="D165" s="92"/>
+      <c r="E165" s="92"/>
+      <c r="F165" s="92"/>
+      <c r="G165" s="92"/>
+      <c r="H165" s="93"/>
+    </row>
+    <row r="166" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B166" s="91"/>
+      <c r="C166" s="92"/>
+      <c r="D166" s="92"/>
+      <c r="E166" s="92"/>
+      <c r="F166" s="92"/>
+      <c r="G166" s="92"/>
+      <c r="H166" s="93"/>
+    </row>
+    <row r="167" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B167" s="91"/>
+      <c r="C167" s="92"/>
+      <c r="D167" s="92"/>
+      <c r="E167" s="92"/>
+      <c r="F167" s="92"/>
+      <c r="G167" s="92"/>
+      <c r="H167" s="93"/>
+    </row>
+    <row r="168" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B168" s="91"/>
+      <c r="C168" s="92"/>
+      <c r="D168" s="92"/>
+      <c r="E168" s="92"/>
+      <c r="F168" s="92"/>
+      <c r="G168" s="92"/>
+      <c r="H168" s="93"/>
+    </row>
+    <row r="169" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B169" s="91"/>
+      <c r="C169" s="92"/>
+      <c r="D169" s="92"/>
+      <c r="E169" s="92"/>
+      <c r="F169" s="92"/>
+      <c r="G169" s="92"/>
+      <c r="H169" s="93"/>
+    </row>
+    <row r="170" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B170" s="91"/>
+      <c r="C170" s="92"/>
+      <c r="D170" s="92"/>
+      <c r="E170" s="92"/>
+      <c r="F170" s="92"/>
+      <c r="G170" s="92"/>
+      <c r="H170" s="93"/>
+    </row>
+    <row r="171" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B171" s="91"/>
+      <c r="C171" s="92"/>
+      <c r="D171" s="92"/>
+      <c r="E171" s="92"/>
+      <c r="F171" s="92"/>
+      <c r="G171" s="92"/>
+      <c r="H171" s="93"/>
+    </row>
+    <row r="172" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B172" s="91"/>
+      <c r="C172" s="92"/>
+      <c r="D172" s="92"/>
+      <c r="E172" s="92"/>
+      <c r="F172" s="92"/>
+      <c r="G172" s="92"/>
+      <c r="H172" s="93"/>
+    </row>
+    <row r="173" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B173" s="91"/>
+      <c r="C173" s="92"/>
+      <c r="D173" s="92"/>
+      <c r="E173" s="92"/>
+      <c r="F173" s="92"/>
+      <c r="G173" s="92"/>
+      <c r="H173" s="93"/>
+    </row>
+    <row r="174" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B174" s="91"/>
+      <c r="C174" s="92"/>
+      <c r="D174" s="92"/>
+      <c r="E174" s="92"/>
+      <c r="F174" s="92"/>
+      <c r="G174" s="92"/>
+      <c r="H174" s="93"/>
+    </row>
+    <row r="175" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B175" s="91"/>
+      <c r="C175" s="92"/>
+      <c r="D175" s="92"/>
+      <c r="E175" s="92"/>
+      <c r="F175" s="92"/>
+      <c r="G175" s="92"/>
+      <c r="H175" s="93"/>
+    </row>
+    <row r="176" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B176" s="91"/>
+      <c r="C176" s="92"/>
+      <c r="D176" s="92"/>
+      <c r="E176" s="92"/>
+      <c r="F176" s="92"/>
+      <c r="G176" s="92"/>
+      <c r="H176" s="93"/>
+    </row>
+    <row r="177" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B177" s="91"/>
+      <c r="C177" s="92"/>
+      <c r="D177" s="92"/>
+      <c r="E177" s="92"/>
+      <c r="F177" s="92"/>
+      <c r="G177" s="92"/>
+      <c r="H177" s="93"/>
+    </row>
+    <row r="178" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B178" s="91"/>
+      <c r="C178" s="92"/>
+      <c r="D178" s="92"/>
+      <c r="E178" s="92"/>
+      <c r="F178" s="92"/>
+      <c r="G178" s="92"/>
+      <c r="H178" s="93"/>
+    </row>
+    <row r="179" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B179" s="91"/>
+      <c r="C179" s="92"/>
+      <c r="D179" s="92"/>
+      <c r="E179" s="92"/>
+      <c r="F179" s="92"/>
+      <c r="G179" s="92"/>
+      <c r="H179" s="93"/>
+    </row>
+    <row r="180" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B180" s="91"/>
+      <c r="C180" s="92"/>
+      <c r="D180" s="92"/>
+      <c r="E180" s="92"/>
+      <c r="F180" s="92"/>
+      <c r="G180" s="92"/>
+      <c r="H180" s="93"/>
+    </row>
+    <row r="181" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B181" s="91"/>
+      <c r="C181" s="92"/>
+      <c r="D181" s="92"/>
+      <c r="E181" s="92"/>
+      <c r="F181" s="92"/>
+      <c r="G181" s="92"/>
+      <c r="H181" s="93"/>
+    </row>
+    <row r="182" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B182" s="91"/>
+      <c r="C182" s="92"/>
+      <c r="D182" s="92"/>
+      <c r="E182" s="92"/>
+      <c r="F182" s="92"/>
+      <c r="G182" s="92"/>
+      <c r="H182" s="93"/>
+    </row>
+    <row r="183" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B183" s="91"/>
+      <c r="C183" s="92"/>
+      <c r="D183" s="92"/>
+      <c r="E183" s="92"/>
+      <c r="F183" s="92"/>
+      <c r="G183" s="92"/>
+      <c r="H183" s="93"/>
+    </row>
+    <row r="184" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B184" s="91"/>
+      <c r="C184" s="92"/>
+      <c r="D184" s="92"/>
+      <c r="E184" s="92"/>
+      <c r="F184" s="92"/>
+      <c r="G184" s="92"/>
+      <c r="H184" s="93"/>
+    </row>
+    <row r="185" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B185" s="91"/>
+      <c r="C185" s="92"/>
+      <c r="D185" s="92"/>
+      <c r="E185" s="92"/>
+      <c r="F185" s="92"/>
+      <c r="G185" s="92"/>
+      <c r="H185" s="93"/>
+    </row>
+    <row r="186" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B186" s="91"/>
+      <c r="C186" s="92"/>
+      <c r="D186" s="92"/>
+      <c r="E186" s="92"/>
+      <c r="F186" s="92"/>
+      <c r="G186" s="92"/>
+      <c r="H186" s="93"/>
+    </row>
+    <row r="187" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B187" s="94"/>
+      <c r="C187" s="95"/>
+      <c r="D187" s="95"/>
+      <c r="E187" s="95"/>
+      <c r="F187" s="95"/>
+      <c r="G187" s="95"/>
+      <c r="H187" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3709,35 +3690,35 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O191"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33" customWidth="1"/>
-    <col min="2" max="2" width="21.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5" customWidth="1"/>
-    <col min="6" max="6" width="31.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="61.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.44140625" customWidth="1"/>
+    <col min="6" max="6" width="31.44140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16.33203125" style="1" customWidth="1"/>
     <col min="8" max="8" width="24.6640625" customWidth="1"/>
-    <col min="9" max="9" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="13" width="11.5" customWidth="1"/>
+    <col min="9" max="9" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="13" width="11.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="94" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" ht="135.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="28" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="64" t="s">
-        <v>224</v>
-      </c>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="64"/>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B1" s="97" t="s">
+        <v>237</v>
+      </c>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
+      <c r="F1" s="97"/>
+      <c r="G1" s="97"/>
+      <c r="H1" s="97"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -3745,7 +3726,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -3753,7 +3734,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -3761,7 +3742,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -3769,7 +3750,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -3778,7 +3759,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -3786,7 +3767,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -3794,7 +3775,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -3802,12 +3783,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="35" t="s">
         <v>15</v>
       </c>
@@ -3848,7 +3829,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="59" t="s">
         <v>23</v>
       </c>
@@ -3892,7 +3873,7 @@
         <v>1.04602785990872</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="59" t="s">
         <v>26</v>
       </c>
@@ -3936,7 +3917,7 @@
         <v>1.0793097188846901</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="59" t="s">
         <v>28</v>
       </c>
@@ -3978,7 +3959,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="59" t="s">
         <v>29</v>
       </c>
@@ -4020,7 +4001,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="59" t="s">
         <v>30</v>
       </c>
@@ -4062,7 +4043,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="59" t="s">
         <v>31</v>
       </c>
@@ -4106,7 +4087,7 @@
         <v>1.0637991288100499</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="59" t="s">
         <v>31</v>
       </c>
@@ -4150,7 +4131,7 @@
         <v>1.0637991288100499</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="59" t="s">
         <v>32</v>
       </c>
@@ -4192,7 +4173,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="59" t="s">
         <v>32</v>
       </c>
@@ -4234,7 +4215,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="59" t="s">
         <v>36</v>
       </c>
@@ -4278,7 +4259,7 @@
         <v>1.0793097188846901</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="59" t="s">
         <v>36</v>
       </c>
@@ -4322,7 +4303,7 @@
         <v>1.0793097188846901</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="59" t="s">
         <v>36</v>
       </c>
@@ -4366,7 +4347,7 @@
         <v>1.1218734375719399</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="59" t="s">
         <v>38</v>
       </c>
@@ -4410,7 +4391,7 @@
         <v>1.1218734375719399</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="59" t="s">
         <v>39</v>
       </c>
@@ -4454,7 +4435,7 @@
         <v>1.1218734375719399</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="59" t="s">
         <v>41</v>
       </c>
@@ -4498,7 +4479,7 @@
         <v>1.0793097188846901</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="59" t="s">
         <v>42</v>
       </c>
@@ -4541,7 +4522,7 @@
       </c>
       <c r="O28" s="2"/>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="59" t="s">
         <v>42</v>
       </c>
@@ -4584,7 +4565,7 @@
       </c>
       <c r="O29" s="2"/>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" s="59" t="s">
         <v>44</v>
       </c>
@@ -4628,7 +4609,7 @@
         <v>1.0793097188846901</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" s="59" t="s">
         <v>44</v>
       </c>
@@ -4672,7 +4653,7 @@
         <v>1.1218734375719399</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" s="59" t="s">
         <v>46</v>
       </c>
@@ -4716,7 +4697,7 @@
         <v>1.0793097188846901</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" s="59" t="s">
         <v>47</v>
       </c>
@@ -4760,7 +4741,7 @@
         <v>1.0793097188846901</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" s="59" t="s">
         <v>47</v>
       </c>
@@ -4804,7 +4785,7 @@
         <v>1.1218734375719399</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" s="59" t="s">
         <v>47</v>
       </c>
@@ -4848,7 +4829,7 @@
         <v>1.1218734375719399</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" s="59" t="s">
         <v>47</v>
       </c>
@@ -4892,7 +4873,7 @@
         <v>1.0793097188846901</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" s="59" t="s">
         <v>49</v>
       </c>
@@ -4936,7 +4917,7 @@
         <v>1.0793097188846901</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" s="59" t="s">
         <v>49</v>
       </c>
@@ -4980,7 +4961,7 @@
         <v>1.0793097188846901</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" s="59" t="s">
         <v>49</v>
       </c>
@@ -5024,7 +5005,7 @@
         <v>1.1218734375719399</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" s="59" t="s">
         <v>49</v>
       </c>
@@ -5068,7 +5049,7 @@
         <v>1.1218734375719399</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" s="59" t="s">
         <v>26</v>
       </c>
@@ -5112,7 +5093,7 @@
         <v>1.0793097188846901</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" s="59" t="s">
         <v>28</v>
       </c>
@@ -5154,7 +5135,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" s="59" t="s">
         <v>29</v>
       </c>
@@ -5196,7 +5177,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" s="59" t="s">
         <v>30</v>
       </c>
@@ -5238,7 +5219,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" s="59" t="s">
         <v>31</v>
       </c>
@@ -5282,7 +5263,7 @@
         <v>1.0637991288100499</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" s="59" t="s">
         <v>31</v>
       </c>
@@ -5326,7 +5307,7 @@
         <v>1.0637991288100499</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47" s="59" t="s">
         <v>36</v>
       </c>
@@ -5370,7 +5351,7 @@
         <v>1.0793097188846901</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" s="59" t="s">
         <v>36</v>
       </c>
@@ -5414,7 +5395,7 @@
         <v>1.0793097188846901</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49" s="59" t="s">
         <v>41</v>
       </c>
@@ -5458,7 +5439,7 @@
         <v>1.0793097188846901</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50" s="59" t="s">
         <v>42</v>
       </c>
@@ -5501,7 +5482,7 @@
       </c>
       <c r="O50" s="2"/>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51" s="59" t="s">
         <v>42</v>
       </c>
@@ -5544,7 +5525,7 @@
       </c>
       <c r="O51" s="2"/>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A52" s="59" t="s">
         <v>44</v>
       </c>
@@ -5588,7 +5569,7 @@
         <v>1.0793097188846901</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A53" s="59" t="s">
         <v>46</v>
       </c>
@@ -5632,7 +5613,7 @@
         <v>1.0793097188846901</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A54" s="59" t="s">
         <v>47</v>
       </c>
@@ -5676,7 +5657,7 @@
         <v>1.0793097188846901</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A55" s="59" t="s">
         <v>47</v>
       </c>
@@ -5720,7 +5701,7 @@
         <v>1.1218734375719399</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A56" s="59" t="s">
         <v>49</v>
       </c>
@@ -5764,7 +5745,7 @@
         <v>1.0793097188846901</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A57" s="59" t="s">
         <v>49</v>
       </c>
@@ -5808,7 +5789,7 @@
         <v>1.0793097188846901</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A58" s="60" t="s">
         <v>50</v>
       </c>
@@ -5852,7 +5833,7 @@
         <v>1.2345580787321599</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A59" s="60" t="s">
         <v>50</v>
       </c>
@@ -5896,7 +5877,7 @@
         <v>1.2539886685866699</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A60" s="60" t="s">
         <v>51</v>
       </c>
@@ -5940,7 +5921,7 @@
         <v>1.2541963802979099</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A61" s="60" t="s">
         <v>52</v>
       </c>
@@ -5984,7 +5965,7 @@
         <v>1.2541963802979099</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A62" s="60" t="s">
         <v>53</v>
       </c>
@@ -6028,7 +6009,7 @@
         <v>1.2541963802979099</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A63" s="60" t="s">
         <v>55</v>
       </c>
@@ -6071,7 +6052,7 @@
       </c>
       <c r="O63" s="2"/>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A64" s="60" t="s">
         <v>56</v>
       </c>
@@ -6114,7 +6095,7 @@
       </c>
       <c r="O64" s="2"/>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A65" s="60" t="s">
         <v>57</v>
       </c>
@@ -6157,7 +6138,7 @@
       </c>
       <c r="O65" s="2"/>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A66" s="60" t="s">
         <v>58</v>
       </c>
@@ -6201,7 +6182,7 @@
         <v>1.2539886685866699</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A67" s="60" t="s">
         <v>59</v>
       </c>
@@ -6245,7 +6226,7 @@
         <v>1.2539886685866699</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A68" s="59" t="s">
         <v>31</v>
       </c>
@@ -6289,7 +6270,7 @@
         <v>1.0637991288100499</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A69" s="59" t="s">
         <v>36</v>
       </c>
@@ -6333,7 +6314,7 @@
         <v>1.0793097188846901</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A70" s="59" t="s">
         <v>36</v>
       </c>
@@ -6377,7 +6358,7 @@
         <v>1.0793097188846901</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A71" s="59" t="s">
         <v>36</v>
       </c>
@@ -6421,7 +6402,7 @@
         <v>1.2541963802979099</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A72" s="59" t="s">
         <v>36</v>
       </c>
@@ -6465,7 +6446,7 @@
         <v>1.2345580787321599</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A73" s="59" t="s">
         <v>36</v>
       </c>
@@ -6509,7 +6490,7 @@
         <v>1.2345580787321599</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A74" s="59" t="s">
         <v>36</v>
       </c>
@@ -6553,7 +6534,7 @@
         <v>1.1046170830204201</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A75" s="59" t="s">
         <v>36</v>
       </c>
@@ -6597,7 +6578,7 @@
         <v>1.10530898683042</v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A76" s="59" t="s">
         <v>36</v>
       </c>
@@ -6641,7 +6622,7 @@
         <v>1.2539886685866699</v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A77" s="60" t="s">
         <v>60</v>
       </c>
@@ -6685,7 +6666,7 @@
         <v>1.2541963802979099</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A78" s="60" t="s">
         <v>44</v>
       </c>
@@ -6729,7 +6710,7 @@
         <v>1.0793097188846901</v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A79" s="60" t="s">
         <v>44</v>
       </c>
@@ -6774,7 +6755,7 @@
       </c>
       <c r="O79" s="2"/>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A80" s="60" t="s">
         <v>39</v>
       </c>
@@ -6819,7 +6800,7 @@
       </c>
       <c r="O80" s="2"/>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A81" s="60" t="s">
         <v>39</v>
       </c>
@@ -6864,7 +6845,7 @@
       </c>
       <c r="O81" s="2"/>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A82" s="60" t="s">
         <v>61</v>
       </c>
@@ -6909,7 +6890,7 @@
       </c>
       <c r="O82" s="2"/>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A83" s="60" t="s">
         <v>61</v>
       </c>
@@ -6954,7 +6935,7 @@
       </c>
       <c r="O83" s="2"/>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A84" s="60" t="s">
         <v>29</v>
       </c>
@@ -6996,7 +6977,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A85" s="59" t="s">
         <v>41</v>
       </c>
@@ -7038,7 +7019,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A86" s="59" t="s">
         <v>42</v>
       </c>
@@ -7081,7 +7062,7 @@
       </c>
       <c r="O86" s="2"/>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A87" s="59" t="s">
         <v>42</v>
       </c>
@@ -7124,7 +7105,7 @@
       </c>
       <c r="O87" s="2"/>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A88" s="60" t="s">
         <v>62</v>
       </c>
@@ -7169,7 +7150,7 @@
       </c>
       <c r="O88" s="2"/>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A89" s="60" t="s">
         <v>63</v>
       </c>
@@ -7212,7 +7193,7 @@
       </c>
       <c r="O89" s="2"/>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A90" s="60" t="s">
         <v>63</v>
       </c>
@@ -7255,7 +7236,7 @@
       </c>
       <c r="O90" s="2"/>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A91" s="60" t="s">
         <v>64</v>
       </c>
@@ -7300,7 +7281,7 @@
       </c>
       <c r="O91" s="2"/>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A92" s="60" t="s">
         <v>65</v>
       </c>
@@ -7345,7 +7326,7 @@
       </c>
       <c r="O92" s="2"/>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A93" s="60" t="s">
         <v>28</v>
       </c>
@@ -7387,7 +7368,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A94" s="60" t="s">
         <v>26</v>
       </c>
@@ -7431,7 +7412,7 @@
         <v>1.0793097188846901</v>
       </c>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A95" s="60" t="s">
         <v>66</v>
       </c>
@@ -7476,7 +7457,7 @@
       </c>
       <c r="O95" s="2"/>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A96" s="60" t="s">
         <v>66</v>
       </c>
@@ -7521,7 +7502,7 @@
       </c>
       <c r="O96" s="2"/>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A97" s="60" t="s">
         <v>46</v>
       </c>
@@ -7566,7 +7547,7 @@
       </c>
       <c r="O97" s="2"/>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A98" s="60" t="s">
         <v>47</v>
       </c>
@@ -7611,7 +7592,7 @@
       </c>
       <c r="O98" s="2"/>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A99" s="60" t="s">
         <v>47</v>
       </c>
@@ -7656,7 +7637,7 @@
       </c>
       <c r="O99" s="2"/>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A100" s="60" t="s">
         <v>49</v>
       </c>
@@ -7700,7 +7681,7 @@
         <v>1.0793097188846901</v>
       </c>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A101" s="60" t="s">
         <v>49</v>
       </c>
@@ -7744,7 +7725,7 @@
         <v>1.0793097188846901</v>
       </c>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A102" s="60" t="s">
         <v>49</v>
       </c>
@@ -7788,7 +7769,7 @@
         <v>1.2539886685866699</v>
       </c>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A103" s="60" t="s">
         <v>49</v>
       </c>
@@ -7832,7 +7813,7 @@
         <v>1.2345580787321599</v>
       </c>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A104" s="60" t="s">
         <v>49</v>
       </c>
@@ -7876,7 +7857,7 @@
         <v>1.2539886685866699</v>
       </c>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A105" s="60" t="s">
         <v>67</v>
       </c>
@@ -7920,7 +7901,7 @@
         <v>1.2541963802979099</v>
       </c>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A106" s="59" t="s">
         <v>36</v>
       </c>
@@ -7964,7 +7945,7 @@
         <v>1.0793097188846901</v>
       </c>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A107" s="59" t="s">
         <v>26</v>
       </c>
@@ -8008,7 +7989,7 @@
         <v>1.0793097188846901</v>
       </c>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A108" s="59" t="s">
         <v>46</v>
       </c>
@@ -8052,7 +8033,7 @@
         <v>1.0793097188846901</v>
       </c>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A109" s="59" t="s">
         <v>49</v>
       </c>
@@ -8096,7 +8077,7 @@
         <v>1.0793097188846901</v>
       </c>
     </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A110" s="59" t="s">
         <v>47</v>
       </c>
@@ -8140,7 +8121,7 @@
         <v>1.0793097188846901</v>
       </c>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A111" s="59" t="s">
         <v>41</v>
       </c>
@@ -8184,7 +8165,7 @@
         <v>1.0793097188846901</v>
       </c>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A112" s="59" t="s">
         <v>36</v>
       </c>
@@ -8228,7 +8209,7 @@
         <v>1.0793097188846901</v>
       </c>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A113" s="59" t="s">
         <v>42</v>
       </c>
@@ -8271,7 +8252,7 @@
       </c>
       <c r="O113" s="2"/>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A114" s="59" t="s">
         <v>44</v>
       </c>
@@ -8315,7 +8296,7 @@
         <v>1.0793097188846901</v>
       </c>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A115" s="59" t="s">
         <v>49</v>
       </c>
@@ -8359,7 +8340,7 @@
         <v>1.0793097188846901</v>
       </c>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A116" s="59" t="s">
         <v>42</v>
       </c>
@@ -8402,7 +8383,7 @@
       </c>
       <c r="O116" s="2"/>
     </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A117" s="59" t="s">
         <v>47</v>
       </c>
@@ -8446,7 +8427,7 @@
         <v>1.0793097188846901</v>
       </c>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A118" s="59" t="s">
         <v>31</v>
       </c>
@@ -8490,7 +8471,7 @@
         <v>1.0637991288100499</v>
       </c>
     </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A119" s="59" t="s">
         <v>29</v>
       </c>
@@ -8532,7 +8513,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A120" s="59" t="s">
         <v>28</v>
       </c>
@@ -8574,7 +8555,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A121" s="59" t="s">
         <v>36</v>
       </c>
@@ -8618,7 +8599,7 @@
         <v>1.0793097188846901</v>
       </c>
     </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A122" s="59" t="s">
         <v>26</v>
       </c>
@@ -8662,7 +8643,7 @@
         <v>1.0793097188846901</v>
       </c>
     </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A123" s="59" t="s">
         <v>46</v>
       </c>
@@ -8706,7 +8687,7 @@
         <v>1.0793097188846901</v>
       </c>
     </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A124" s="59" t="s">
         <v>49</v>
       </c>
@@ -8750,7 +8731,7 @@
         <v>1.0793097188846901</v>
       </c>
     </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A125" s="59" t="s">
         <v>47</v>
       </c>
@@ -8794,7 +8775,7 @@
         <v>1.0793097188846901</v>
       </c>
     </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A126" s="59" t="s">
         <v>68</v>
       </c>
@@ -8838,7 +8819,7 @@
         <v>1.1218999999999999</v>
       </c>
     </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A127" s="59" t="s">
         <v>36</v>
       </c>
@@ -8882,7 +8863,7 @@
         <v>1.1218999999999999</v>
       </c>
     </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A128" s="59" t="s">
         <v>44</v>
       </c>
@@ -8926,7 +8907,7 @@
         <v>1.1218999999999999</v>
       </c>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A129" s="59" t="s">
         <v>49</v>
       </c>
@@ -8970,7 +8951,7 @@
         <v>1.1218734375719399</v>
       </c>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A130" s="59" t="s">
         <v>69</v>
       </c>
@@ -9012,7 +8993,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A131" s="59" t="s">
         <v>47</v>
       </c>
@@ -9056,7 +9037,7 @@
         <v>1.1218734375719399</v>
       </c>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A132" s="59" t="s">
         <v>70</v>
       </c>
@@ -9100,7 +9081,7 @@
         <v>1.0637991288100499</v>
       </c>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A133" s="59" t="s">
         <v>71</v>
       </c>
@@ -9142,7 +9123,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A134" s="59" t="s">
         <v>72</v>
       </c>
@@ -9184,7 +9165,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A135" s="59" t="s">
         <v>73</v>
       </c>
@@ -9226,7 +9207,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A136" s="59" t="s">
         <v>74</v>
       </c>
@@ -9270,7 +9251,7 @@
         <v>1.04602785990872</v>
       </c>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A137" s="59" t="s">
         <v>75</v>
       </c>
@@ -9314,7 +9295,7 @@
         <v>1.04602785990872</v>
       </c>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A138" s="59" t="s">
         <v>76</v>
       </c>
@@ -9358,7 +9339,7 @@
         <v>1.04602785990872</v>
       </c>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A139" s="59" t="s">
         <v>77</v>
       </c>
@@ -9400,7 +9381,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A140" s="60" t="s">
         <v>50</v>
       </c>
@@ -9444,7 +9425,7 @@
         <v>1.2345580787321599</v>
       </c>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A141" s="60" t="s">
         <v>78</v>
       </c>
@@ -9488,7 +9469,7 @@
         <v>1.10530898683042</v>
       </c>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A142" s="60" t="s">
         <v>36</v>
       </c>
@@ -9532,7 +9513,7 @@
         <v>1.10530898683042</v>
       </c>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A143" s="60" t="s">
         <v>36</v>
       </c>
@@ -9576,7 +9557,7 @@
         <v>1.10530898683042</v>
       </c>
     </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A144" s="60" t="s">
         <v>36</v>
       </c>
@@ -9620,7 +9601,7 @@
         <v>1.10530898683042</v>
       </c>
     </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A145" s="60" t="s">
         <v>36</v>
       </c>
@@ -9664,7 +9645,7 @@
         <v>1.2275250649631799</v>
       </c>
     </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A146" s="60" t="s">
         <v>36</v>
       </c>
@@ -9708,7 +9689,7 @@
         <v>1.10530898683042</v>
       </c>
     </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A147" s="60" t="s">
         <v>36</v>
       </c>
@@ -9752,7 +9733,7 @@
         <v>1.0764349399111499</v>
       </c>
     </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A148" s="60" t="s">
         <v>36</v>
       </c>
@@ -9796,7 +9777,7 @@
         <v>1.0764349399111499</v>
       </c>
     </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A149" s="60" t="s">
         <v>36</v>
       </c>
@@ -9840,7 +9821,7 @@
         <v>1.0654986309886401</v>
       </c>
     </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A150" s="60" t="s">
         <v>36</v>
       </c>
@@ -9884,7 +9865,7 @@
         <v>1.0793097188846901</v>
       </c>
     </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A151" s="60" t="s">
         <v>79</v>
       </c>
@@ -9927,7 +9908,7 @@
       </c>
       <c r="O151" s="2"/>
     </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A152" s="60" t="s">
         <v>44</v>
       </c>
@@ -9971,7 +9952,7 @@
         <v>1.04602785990872</v>
       </c>
     </row>
-    <row r="153" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A153" s="60" t="s">
         <v>61</v>
       </c>
@@ -10015,7 +9996,7 @@
         <v>1.2345580787321599</v>
       </c>
     </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A154" s="60" t="s">
         <v>61</v>
       </c>
@@ -10059,7 +10040,7 @@
         <v>1.2345580787321599</v>
       </c>
     </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A155" s="60" t="s">
         <v>80</v>
       </c>
@@ -10103,7 +10084,7 @@
         <v>1.10530898683042</v>
       </c>
     </row>
-    <row r="156" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A156" s="60" t="s">
         <v>62</v>
       </c>
@@ -10147,7 +10128,7 @@
         <v>1.10530898683042</v>
       </c>
     </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A157" s="60" t="s">
         <v>63</v>
       </c>
@@ -10190,7 +10171,7 @@
       </c>
       <c r="O157" s="2"/>
     </row>
-    <row r="158" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A158" s="60" t="s">
         <v>81</v>
       </c>
@@ -10234,7 +10215,7 @@
         <v>1.0384707228569501</v>
       </c>
     </row>
-    <row r="159" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A159" s="60" t="s">
         <v>81</v>
       </c>
@@ -10278,7 +10259,7 @@
         <v>1.0384707228569501</v>
       </c>
     </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A160" s="60" t="s">
         <v>81</v>
       </c>
@@ -10322,7 +10303,7 @@
         <v>1.0384707228569501</v>
       </c>
     </row>
-    <row r="161" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A161" s="60" t="s">
         <v>44</v>
       </c>
@@ -10366,7 +10347,7 @@
         <v>1.04602785990872</v>
       </c>
     </row>
-    <row r="162" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A162" s="60" t="s">
         <v>82</v>
       </c>
@@ -10410,7 +10391,7 @@
         <v>1.0384707228569501</v>
       </c>
     </row>
-    <row r="163" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A163" s="60" t="s">
         <v>66</v>
       </c>
@@ -10454,7 +10435,7 @@
         <v>1.2345580787321599</v>
       </c>
     </row>
-    <row r="164" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A164" s="60" t="s">
         <v>66</v>
       </c>
@@ -10498,7 +10479,7 @@
         <v>1.10530898683042</v>
       </c>
     </row>
-    <row r="165" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A165" s="60" t="s">
         <v>66</v>
       </c>
@@ -10542,7 +10523,7 @@
         <v>1.2345580787321599</v>
       </c>
     </row>
-    <row r="166" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A166" s="60" t="s">
         <v>49</v>
       </c>
@@ -10586,7 +10567,7 @@
         <v>1.10530898683042</v>
       </c>
     </row>
-    <row r="167" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A167" s="60" t="s">
         <v>49</v>
       </c>
@@ -10630,7 +10611,7 @@
         <v>1.2345580787321599</v>
       </c>
     </row>
-    <row r="168" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A168" s="59" t="str">
         <f>B4</f>
         <v>RU1 Power module</v>
@@ -10674,8 +10655,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="169" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="170" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="170" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A170" s="1" t="s">
         <v>2</v>
       </c>
@@ -10683,7 +10664,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="171" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>4</v>
       </c>
@@ -10691,7 +10672,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="172" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>6</v>
       </c>
@@ -10699,7 +10680,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="173" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>8</v>
       </c>
@@ -10707,7 +10688,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>9</v>
       </c>
@@ -10715,7 +10696,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="175" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>11</v>
       </c>
@@ -10723,7 +10704,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="176" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>13</v>
       </c>
@@ -10731,12 +10712,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A177" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="178" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A178" s="35" t="s">
         <v>15</v>
       </c>
@@ -10777,7 +10758,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="179" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A179" s="55" t="s">
         <v>86</v>
       </c>
@@ -10821,7 +10802,7 @@
         <v>1.04602785990872</v>
       </c>
     </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A180" s="56" t="s">
         <v>87</v>
       </c>
@@ -10865,7 +10846,7 @@
         <v>1.04602785990872</v>
       </c>
     </row>
-    <row r="181" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A181" s="55" t="s">
         <v>31</v>
       </c>
@@ -10909,7 +10890,7 @@
         <v>1.04602785990872</v>
       </c>
     </row>
-    <row r="182" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A182" s="55" t="s">
         <v>88</v>
       </c>
@@ -10953,7 +10934,7 @@
         <v>1.04602785990872</v>
       </c>
     </row>
-    <row r="183" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A183" s="55" t="s">
         <v>89</v>
       </c>
@@ -10997,7 +10978,7 @@
         <v>1.04602785990872</v>
       </c>
     </row>
-    <row r="184" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A184" s="55" t="s">
         <v>90</v>
       </c>
@@ -11041,7 +11022,7 @@
         <v>1.04602785990872</v>
       </c>
     </row>
-    <row r="185" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A185" s="55" t="s">
         <v>91</v>
       </c>
@@ -11085,7 +11066,7 @@
         <v>1.04602785990872</v>
       </c>
     </row>
-    <row r="186" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A186" s="55" t="s">
         <v>92</v>
       </c>
@@ -11129,7 +11110,7 @@
         <v>1.04602785990872</v>
       </c>
     </row>
-    <row r="187" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A187" s="55" t="s">
         <v>93</v>
       </c>
@@ -11173,7 +11154,7 @@
         <v>1.04602785990872</v>
       </c>
     </row>
-    <row r="188" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A188" s="55" t="s">
         <v>68</v>
       </c>
@@ -11217,7 +11198,7 @@
         <v>1.04602785990872</v>
       </c>
     </row>
-    <row r="189" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A189" s="55" t="s">
         <v>94</v>
       </c>
@@ -11260,7 +11241,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="190" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A190" s="56" t="str">
         <f>B170</f>
         <v>RU2 DC link capacitor</v>
@@ -11304,7 +11285,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="191" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="191" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B1:H1"/>
@@ -11318,17 +11299,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:O24"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.1640625" customWidth="1"/>
-    <col min="6" max="6" width="31.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.1640625" customWidth="1"/>
+    <col min="3" max="3" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.109375" customWidth="1"/>
+    <col min="6" max="6" width="31.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -11337,7 +11318,7 @@
       </c>
       <c r="G1" s="1"/>
     </row>
-    <row r="2" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -11346,7 +11327,7 @@
       </c>
       <c r="G2" s="1"/>
     </row>
-    <row r="3" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -11355,7 +11336,7 @@
       </c>
       <c r="G3" s="1"/>
     </row>
-    <row r="4" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -11365,7 +11346,7 @@
       </c>
       <c r="G4" s="1"/>
     </row>
-    <row r="5" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -11374,7 +11355,7 @@
       </c>
       <c r="G5" s="1"/>
     </row>
-    <row r="6" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -11383,7 +11364,7 @@
       </c>
       <c r="G6" s="1"/>
     </row>
-    <row r="7" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -11392,13 +11373,13 @@
       </c>
       <c r="G7" s="1"/>
     </row>
-    <row r="8" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G8" s="1"/>
     </row>
-    <row r="9" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="35" t="s">
         <v>15</v>
       </c>
@@ -11439,7 +11420,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="55" t="s">
         <v>97</v>
       </c>
@@ -11481,7 +11462,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="56" t="str">
         <f>B1</f>
         <v>Energy per hours RU1</v>
@@ -11527,11 +11508,11 @@
       <c r="N11" s="4"/>
       <c r="O11" s="6"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="7"/>
       <c r="B12" s="3"/>
     </row>
-    <row r="13" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>2</v>
       </c>
@@ -11540,7 +11521,7 @@
       </c>
       <c r="G13" s="1"/>
     </row>
-    <row r="14" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -11549,7 +11530,7 @@
       </c>
       <c r="G14" s="1"/>
     </row>
-    <row r="15" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>6</v>
       </c>
@@ -11558,7 +11539,7 @@
       </c>
       <c r="G15" s="1"/>
     </row>
-    <row r="16" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>8</v>
       </c>
@@ -11568,7 +11549,7 @@
       </c>
       <c r="G16" s="1"/>
     </row>
-    <row r="17" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>9</v>
       </c>
@@ -11577,7 +11558,7 @@
       </c>
       <c r="G17" s="1"/>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>11</v>
       </c>
@@ -11585,7 +11566,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>13</v>
       </c>
@@ -11594,13 +11575,13 @@
       </c>
       <c r="G19" s="1"/>
     </row>
-    <row r="20" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G20" s="1"/>
     </row>
-    <row r="21" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="35" t="s">
         <v>15</v>
       </c>
@@ -11641,7 +11622,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="55" t="s">
         <v>97</v>
       </c>
@@ -11683,7 +11664,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="56" t="str">
         <f>B13</f>
         <v>Energy per hours RU2</v>
@@ -11729,7 +11710,7 @@
       <c r="N23" s="4"/>
       <c r="O23" s="6"/>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B24" s="8"/>
       <c r="J24" s="5"/>
       <c r="K24" s="5"/>
@@ -11745,14 +11726,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="77.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="77.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="86.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>100</v>
       </c>
@@ -11760,21 +11741,21 @@
         <v>101</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
         <v>102</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C2" s="12" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C3" s="13"/>
     </row>
-    <row r="4" spans="1:3" ht="48" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
         <v>104</v>
       </c>
@@ -11785,7 +11766,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="48" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>107</v>
       </c>
@@ -11797,10 +11778,10 @@
         <v>108</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C6" s="13"/>
     </row>
-    <row r="7" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>109</v>
       </c>
@@ -11811,21 +11792,21 @@
         <v>110</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
         <v>111</v>
       </c>
       <c r="B8" s="34" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C8" s="13" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C9" s="13"/>
     </row>
-    <row r="10" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
         <v>113</v>
       </c>
@@ -11836,7 +11817,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>116</v>
       </c>
@@ -11862,16 +11843,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="62.5" customWidth="1"/>
-    <col min="4" max="4" width="69.83203125" customWidth="1"/>
-    <col min="5" max="5" width="18.5" customWidth="1"/>
+    <col min="2" max="2" width="16.77734375" customWidth="1"/>
+    <col min="3" max="3" width="62.44140625" customWidth="1"/>
+    <col min="4" max="4" width="69.77734375" customWidth="1"/>
+    <col min="5" max="5" width="18.44140625" customWidth="1"/>
     <col min="6" max="6" width="84.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>100</v>
       </c>
@@ -11879,7 +11860,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>118</v>
       </c>
@@ -11899,7 +11880,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="17" t="s">
         <v>124</v>
       </c>
@@ -11917,7 +11898,7 @@
       </c>
       <c r="F3" s="32"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
         <v>129</v>
       </c>
@@ -11935,7 +11916,7 @@
       </c>
       <c r="F4" s="32"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
         <v>133</v>
       </c>
@@ -11953,7 +11934,7 @@
       </c>
       <c r="F5" s="32"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
         <v>137</v>
       </c>
@@ -11971,7 +11952,7 @@
       </c>
       <c r="F6" s="32"/>
     </row>
-    <row r="7" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="s">
         <v>139</v>
       </c>
@@ -11989,7 +11970,7 @@
       </c>
       <c r="F7" s="32"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="s">
         <v>143</v>
       </c>
@@ -12007,7 +11988,7 @@
       </c>
       <c r="F8" s="32"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="17" t="s">
         <v>147</v>
       </c>
@@ -12025,7 +12006,7 @@
       </c>
       <c r="F9" s="32"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="17" t="s">
         <v>151</v>
       </c>
@@ -12043,7 +12024,7 @@
       </c>
       <c r="F10" s="32"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="17" t="s">
         <v>155</v>
       </c>
@@ -12061,7 +12042,7 @@
       </c>
       <c r="F11" s="32"/>
     </row>
-    <row r="12" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
         <v>158</v>
       </c>
@@ -12079,7 +12060,7 @@
       </c>
       <c r="F12" s="32"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="17" t="s">
         <v>162</v>
       </c>
@@ -12097,7 +12078,7 @@
       </c>
       <c r="F13" s="32"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="17" t="s">
         <v>166</v>
       </c>
@@ -12115,7 +12096,7 @@
       </c>
       <c r="F14" s="32"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
         <v>170</v>
       </c>
@@ -12133,7 +12114,7 @@
       </c>
       <c r="F15" s="32"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="17" t="s">
         <v>174</v>
       </c>
@@ -12151,7 +12132,7 @@
       </c>
       <c r="F16" s="32"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="17" t="s">
         <v>178</v>
       </c>
@@ -12169,7 +12150,7 @@
       </c>
       <c r="F17" s="32"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="17" t="s">
         <v>182</v>
       </c>
@@ -12196,32 +12177,32 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.1640625" customWidth="1"/>
+    <col min="1" max="1" width="16.109375" customWidth="1"/>
     <col min="2" max="2" width="18.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="24.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="97.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" ht="97.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="28" t="s">
         <v>101</v>
       </c>
-      <c r="B2" s="65" t="s">
-        <v>227</v>
-      </c>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B2" s="98" t="s">
+        <v>226</v>
+      </c>
+      <c r="C2" s="98"/>
+      <c r="D2" s="98"/>
+      <c r="E2" s="98"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="19"/>
       <c r="B5" s="20" t="s">
         <v>186</v>
@@ -12236,7 +12217,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="20" t="s">
         <v>189</v>
       </c>
@@ -12253,7 +12234,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="20" t="s">
         <v>190</v>
       </c>
@@ -12286,14 +12267,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.5" customWidth="1"/>
+    <col min="1" max="1" width="30.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.44140625" customWidth="1"/>
     <col min="3" max="3" width="138.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>100</v>
       </c>
@@ -12301,10 +12282,10 @@
         <v>101</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C2" s="19"/>
     </row>
-    <row r="3" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
         <v>191</v>
       </c>
@@ -12315,7 +12296,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="22" t="s">
         <v>193</v>
       </c>
@@ -12326,7 +12307,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="22" t="s">
         <v>195</v>
       </c>
@@ -12337,10 +12318,10 @@
         <v>196</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C6" s="13"/>
     </row>
-    <row r="7" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="22" t="s">
         <v>197</v>
       </c>
@@ -12351,7 +12332,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="22" t="s">
         <v>200</v>
       </c>
@@ -12362,7 +12343,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="22" t="s">
         <v>201</v>
       </c>
@@ -12373,11 +12354,11 @@
         <v>199</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B10" s="25"/>
       <c r="C10" s="24"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="22" t="s">
         <v>202</v>
       </c>
@@ -12388,10 +12369,10 @@
         <v>203</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C12" s="13"/>
     </row>
-    <row r="13" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="22" t="s">
         <v>204</v>
       </c>
@@ -12402,10 +12383,10 @@
         <v>205</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C14" s="13"/>
     </row>
-    <row r="15" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="22" t="s">
         <v>206</v>
       </c>
@@ -12431,38 +12412,38 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:H6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.83203125" customWidth="1"/>
+    <col min="1" max="1" width="16.77734375" customWidth="1"/>
     <col min="2" max="2" width="23" customWidth="1"/>
-    <col min="3" max="3" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="27.1640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="22.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="77.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" ht="77.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="33" t="s">
         <v>101</v>
       </c>
-      <c r="B2" s="66" t="s">
+      <c r="B2" s="99" t="s">
         <v>216</v>
       </c>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="66"/>
-      <c r="H2" s="66"/>
-    </row>
-    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C2" s="99"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="99"/>
+      <c r="H2" s="99"/>
+    </row>
+    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="21"/>
       <c r="B3" s="29"/>
       <c r="C3" s="29"/>
@@ -12471,7 +12452,7 @@
       <c r="F3" s="29"/>
       <c r="G3" s="29"/>
     </row>
-    <row r="4" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="30" t="s">
         <v>217</v>
       </c>
@@ -12494,7 +12475,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="30" t="s">
         <v>212</v>
       </c>
@@ -12520,7 +12501,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="30" t="s">
         <v>213</v>
       </c>
@@ -12558,30 +12539,30 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.33203125" customWidth="1"/>
-    <col min="2" max="3" width="31.5" customWidth="1"/>
+    <col min="2" max="3" width="31.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="126" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" ht="126" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="33" t="s">
         <v>101</v>
       </c>
-      <c r="B2" s="67" t="s">
-        <v>228</v>
-      </c>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="69"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B2" s="100" t="s">
+        <v>227</v>
+      </c>
+      <c r="C2" s="101"/>
+      <c r="D2" s="101"/>
+      <c r="E2" s="101"/>
+      <c r="F2" s="102"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B4" s="30" t="s">
         <v>212</v>
       </c>
@@ -12589,7 +12570,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="30" t="s">
         <v>214</v>
       </c>
@@ -12600,7 +12581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="30" t="s">
         <v>215</v>
       </c>
